--- a/research/traditional_assets/database/data/norway/norway_chemical_basic.xlsx
+++ b/research/traditional_assets/database/data/norway/norway_chemical_basic.xlsx
@@ -1270,13 +1270,13 @@
         <v>448.9</v>
       </c>
       <c r="L2">
-        <v>776.898603485508</v>
+        <v>776.898603485507</v>
       </c>
       <c r="M2">
         <v>1033.8</v>
       </c>
       <c r="N2">
-        <v>924.239603485508</v>
+        <v>924.239603485507</v>
       </c>
       <c r="O2">
         <v>673.2</v>
@@ -1310,7 +1310,7 @@
         <v>0.13086288311252</v>
       </c>
       <c r="X2">
-        <v>0.0931328611712917</v>
+        <v>0.0931328611712918</v>
       </c>
       <c r="Y2">
         <v>1.96450076472333</v>
@@ -1397,7 +1397,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1534,22 +1534,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.08500419409238885</v>
+        <v>0.0848522848653856</v>
       </c>
       <c r="C2">
-        <v>962.6384177970725</v>
+        <v>954.452330089179</v>
       </c>
       <c r="D2">
-        <v>874.3384177970726</v>
+        <v>877.373330089179</v>
       </c>
       <c r="E2">
-        <v>-673.2</v>
+        <v>-661.979</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>11.221</v>
       </c>
       <c r="G2">
         <v>88.3</v>
@@ -1570,28 +1570,28 @@
         <v>59.93333333333334</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.5644163</v>
       </c>
       <c r="N2">
-        <v>59.93333333333334</v>
+        <v>59.36891703333334</v>
       </c>
       <c r="O2">
-        <v>13.18533333333333</v>
+        <v>13.06116174733334</v>
       </c>
       <c r="P2">
-        <v>46.748</v>
+        <v>46.307755286</v>
       </c>
       <c r="Q2">
-        <v>120.648</v>
+        <v>120.207755286</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.08500419409238885</v>
+        <v>0.08531307562160161</v>
       </c>
       <c r="T2">
-        <v>0.9054086395470866</v>
+        <v>0.9125421621616999</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1608,7 +1608,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>106.1863970500734</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1616,22 +1616,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.0848522848653856</v>
+        <v>0.08470037563838234</v>
       </c>
       <c r="C3">
-        <v>954.452330089179</v>
+        <v>946.2873847101355</v>
       </c>
       <c r="D3">
-        <v>877.373330089179</v>
+        <v>880.4293847101355</v>
       </c>
       <c r="E3">
-        <v>-661.979</v>
+        <v>-650.758</v>
       </c>
       <c r="F3">
-        <v>11.221</v>
+        <v>22.442</v>
       </c>
       <c r="G3">
         <v>88.3</v>
@@ -1652,28 +1652,28 @@
         <v>59.93333333333334</v>
       </c>
       <c r="M3">
-        <v>0.5644163</v>
+        <v>1.1288326</v>
       </c>
       <c r="N3">
-        <v>59.36891703333334</v>
+        <v>58.80450073333333</v>
       </c>
       <c r="O3">
-        <v>13.06116174733334</v>
+        <v>12.93699016133333</v>
       </c>
       <c r="P3">
-        <v>46.307755286</v>
+        <v>45.867510572</v>
       </c>
       <c r="Q3">
-        <v>120.207755286</v>
+        <v>119.767510572</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.08531307562160161</v>
+        <v>0.08562826085549219</v>
       </c>
       <c r="T3">
-        <v>0.9125421621616999</v>
+        <v>0.9198212668704892</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1690,7 +1690,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>106.1863970500734</v>
+        <v>53.09319852503669</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1698,22 +1698,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.08470037563838234</v>
+        <v>0.08454846641137909</v>
       </c>
       <c r="C4">
-        <v>946.2873847101355</v>
+        <v>938.1438033601653</v>
       </c>
       <c r="D4">
-        <v>880.4293847101355</v>
+        <v>883.5068033601653</v>
       </c>
       <c r="E4">
-        <v>-650.758</v>
+        <v>-639.537</v>
       </c>
       <c r="F4">
-        <v>22.442</v>
+        <v>33.663</v>
       </c>
       <c r="G4">
         <v>88.3</v>
@@ -1734,28 +1734,28 @@
         <v>59.93333333333334</v>
       </c>
       <c r="M4">
-        <v>1.1288326</v>
+        <v>1.6932489</v>
       </c>
       <c r="N4">
-        <v>58.80450073333333</v>
+        <v>58.24008443333334</v>
       </c>
       <c r="O4">
-        <v>12.93699016133333</v>
+        <v>12.81281857533333</v>
       </c>
       <c r="P4">
-        <v>45.867510572</v>
+        <v>45.427265858</v>
       </c>
       <c r="Q4">
-        <v>119.767510572</v>
+        <v>119.327265858</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.08562826085549219</v>
+        <v>0.08594994475399906</v>
       </c>
       <c r="T4">
-        <v>0.9198212668704892</v>
+        <v>0.9272504562124493</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1772,7 +1772,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>53.09319852503669</v>
+        <v>35.3954656833578</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1780,22 +1780,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.08454846641137909</v>
+        <v>0.08439655718437583</v>
       </c>
       <c r="C5">
-        <v>938.1438033601653</v>
+        <v>930.0218108500541</v>
       </c>
       <c r="D5">
-        <v>883.5068033601653</v>
+        <v>886.6058108500541</v>
       </c>
       <c r="E5">
-        <v>-639.537</v>
+        <v>-628.316</v>
       </c>
       <c r="F5">
-        <v>33.663</v>
+        <v>44.884</v>
       </c>
       <c r="G5">
         <v>88.3</v>
@@ -1816,28 +1816,28 @@
         <v>59.93333333333334</v>
       </c>
       <c r="M5">
-        <v>1.6932489</v>
+        <v>2.2576652</v>
       </c>
       <c r="N5">
-        <v>58.24008443333334</v>
+        <v>57.67566813333334</v>
       </c>
       <c r="O5">
-        <v>12.81281857533333</v>
+        <v>12.68864698933333</v>
       </c>
       <c r="P5">
-        <v>45.427265858</v>
+        <v>44.987021144</v>
       </c>
       <c r="Q5">
-        <v>119.327265858</v>
+        <v>118.887021144</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.08594994475399906</v>
+        <v>0.08627833040039148</v>
       </c>
       <c r="T5">
-        <v>0.9272504562124493</v>
+        <v>0.9348344203323669</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1854,7 +1854,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>35.3954656833578</v>
+        <v>26.54659926251835</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1862,22 +1862,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.08439655718437583</v>
+        <v>0.08424464795737256</v>
       </c>
       <c r="C6">
-        <v>930.0218108500541</v>
+        <v>921.9216351558946</v>
       </c>
       <c r="D6">
-        <v>886.6058108500541</v>
+        <v>889.7266351558947</v>
       </c>
       <c r="E6">
-        <v>-628.316</v>
+        <v>-617.095</v>
       </c>
       <c r="F6">
-        <v>44.884</v>
+        <v>56.105</v>
       </c>
       <c r="G6">
         <v>88.3</v>
@@ -1898,28 +1898,28 @@
         <v>59.93333333333334</v>
       </c>
       <c r="M6">
-        <v>2.2576652</v>
+        <v>2.8220815</v>
       </c>
       <c r="N6">
-        <v>57.67566813333334</v>
+        <v>57.11125183333333</v>
       </c>
       <c r="O6">
-        <v>12.68864698933333</v>
+        <v>12.56447540333333</v>
       </c>
       <c r="P6">
-        <v>44.987021144</v>
+        <v>44.54677643</v>
       </c>
       <c r="Q6">
-        <v>118.887021144</v>
+        <v>118.44677643</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.08627833040039148</v>
+        <v>0.08661362942881323</v>
       </c>
       <c r="T6">
-        <v>0.9348344203323669</v>
+        <v>0.9425780468548092</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1936,7 +1936,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>26.54659926251835</v>
+        <v>21.23727941001468</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1944,22 +1944,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.08424464795737256</v>
+        <v>0.08409273873036932</v>
       </c>
       <c r="C7">
-        <v>921.9216351558946</v>
+        <v>913.8435074749918</v>
       </c>
       <c r="D7">
-        <v>889.7266351558947</v>
+        <v>892.8695074749919</v>
       </c>
       <c r="E7">
-        <v>-617.095</v>
+        <v>-605.874</v>
       </c>
       <c r="F7">
-        <v>56.105</v>
+        <v>67.32599999999999</v>
       </c>
       <c r="G7">
         <v>88.3</v>
@@ -1980,28 +1980,28 @@
         <v>59.93333333333334</v>
       </c>
       <c r="M7">
-        <v>2.8220815</v>
+        <v>3.386497799999999</v>
       </c>
       <c r="N7">
-        <v>57.11125183333333</v>
+        <v>56.54683553333334</v>
       </c>
       <c r="O7">
-        <v>12.56447540333333</v>
+        <v>12.44030381733333</v>
       </c>
       <c r="P7">
-        <v>44.54677643</v>
+        <v>44.10653171600001</v>
       </c>
       <c r="Q7">
-        <v>118.44677643</v>
+        <v>118.006531716</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.08661362942881323</v>
+        <v>0.0869560624791163</v>
       </c>
       <c r="T7">
-        <v>0.9425780468548092</v>
+        <v>0.9504864313883671</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -2018,7 +2018,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>21.23727941001468</v>
+        <v>17.6977328416789</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2026,22 +2026,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.08409273873036932</v>
+        <v>0.08394082950336607</v>
       </c>
       <c r="C8">
-        <v>913.8435074749918</v>
+        <v>905.7876622829598</v>
       </c>
       <c r="D8">
-        <v>892.8695074749919</v>
+        <v>896.0346622829599</v>
       </c>
       <c r="E8">
-        <v>-605.874</v>
+        <v>-594.653</v>
       </c>
       <c r="F8">
-        <v>67.32599999999999</v>
+        <v>78.54699999999998</v>
       </c>
       <c r="G8">
         <v>88.3</v>
@@ -2062,28 +2062,28 @@
         <v>59.93333333333334</v>
       </c>
       <c r="M8">
-        <v>3.386497799999999</v>
+        <v>3.950914099999999</v>
       </c>
       <c r="N8">
-        <v>56.54683553333334</v>
+        <v>55.98241923333334</v>
       </c>
       <c r="O8">
-        <v>12.44030381733333</v>
+        <v>12.31613223133333</v>
       </c>
       <c r="P8">
-        <v>44.10653171600001</v>
+        <v>43.666287002</v>
       </c>
       <c r="Q8">
-        <v>118.006531716</v>
+        <v>117.566287002</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.0869560624791163</v>
+        <v>0.08730585968103877</v>
       </c>
       <c r="T8">
-        <v>0.9504864313883671</v>
+        <v>0.9585648887075929</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -2100,7 +2100,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>17.6977328416789</v>
+        <v>15.16948529286763</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2108,22 +2108,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.08394082950336607</v>
+        <v>0.0837889202763628</v>
       </c>
       <c r="C9">
-        <v>905.7876622829598</v>
+        <v>897.7543373920336</v>
       </c>
       <c r="D9">
-        <v>896.0346622829599</v>
+        <v>899.2223373920336</v>
       </c>
       <c r="E9">
-        <v>-594.653</v>
+        <v>-583.432</v>
       </c>
       <c r="F9">
-        <v>78.547</v>
+        <v>89.768</v>
       </c>
       <c r="G9">
         <v>88.3</v>
@@ -2144,28 +2144,28 @@
         <v>59.93333333333334</v>
       </c>
       <c r="M9">
-        <v>3.9509141</v>
+        <v>4.5153304</v>
       </c>
       <c r="N9">
-        <v>55.98241923333334</v>
+        <v>55.41800293333334</v>
       </c>
       <c r="O9">
-        <v>12.31613223133333</v>
+        <v>12.19196064533334</v>
       </c>
       <c r="P9">
-        <v>43.666287002</v>
+        <v>43.226042288</v>
       </c>
       <c r="Q9">
-        <v>117.566287002</v>
+        <v>117.126042288</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.08730585968103878</v>
+        <v>0.08766326116995957</v>
       </c>
       <c r="T9">
-        <v>0.958564888707593</v>
+        <v>0.9668189646641934</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2182,7 +2182,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>15.16948529286763</v>
+        <v>13.27329963125917</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2190,22 +2190,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.0837889202763628</v>
+        <v>0.08374231104935954</v>
       </c>
       <c r="C10">
-        <v>897.7543373920336</v>
+        <v>887.5159410576149</v>
       </c>
       <c r="D10">
-        <v>899.2223373920336</v>
+        <v>900.204941057615</v>
       </c>
       <c r="E10">
-        <v>-583.432</v>
+        <v>-572.211</v>
       </c>
       <c r="F10">
-        <v>89.768</v>
+        <v>100.989</v>
       </c>
       <c r="G10">
         <v>88.3</v>
@@ -2226,45 +2226,45 @@
         <v>59.93333333333334</v>
       </c>
       <c r="M10">
-        <v>4.5153304</v>
+        <v>5.2312302</v>
       </c>
       <c r="N10">
-        <v>55.41800293333334</v>
+        <v>54.70210313333334</v>
       </c>
       <c r="O10">
-        <v>12.19196064533334</v>
+        <v>12.03446268933333</v>
       </c>
       <c r="P10">
-        <v>43.226042288</v>
+        <v>42.667640444</v>
       </c>
       <c r="Q10">
-        <v>117.126042288</v>
+        <v>116.567640444</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.08766326116995957</v>
+        <v>0.08802851763665884</v>
       </c>
       <c r="T10">
-        <v>0.9668189646641934</v>
+        <v>0.9752544488835762</v>
       </c>
       <c r="U10">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V10">
         <v>0.22</v>
       </c>
       <c r="W10">
-        <v>0.039234</v>
+        <v>0.040404</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y10">
-        <v>13.27329963125917</v>
+        <v>11.45683348695558</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2272,22 +2272,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.08374231104935954</v>
+        <v>0.08360210182235629</v>
       </c>
       <c r="C11">
-        <v>887.5159410576149</v>
+        <v>879.2637846022749</v>
       </c>
       <c r="D11">
-        <v>900.204941057615</v>
+        <v>903.173784602275</v>
       </c>
       <c r="E11">
-        <v>-572.211</v>
+        <v>-560.99</v>
       </c>
       <c r="F11">
-        <v>100.989</v>
+        <v>112.21</v>
       </c>
       <c r="G11">
         <v>88.3</v>
@@ -2308,28 +2308,28 @@
         <v>59.93333333333334</v>
       </c>
       <c r="M11">
-        <v>5.2312302</v>
+        <v>5.812477999999999</v>
       </c>
       <c r="N11">
-        <v>54.70210313333334</v>
+        <v>54.12085533333334</v>
       </c>
       <c r="O11">
-        <v>12.03446268933333</v>
+        <v>11.90658817333333</v>
       </c>
       <c r="P11">
-        <v>42.667640444</v>
+        <v>42.21426716000001</v>
       </c>
       <c r="Q11">
-        <v>116.567640444</v>
+        <v>116.11426716</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.08802851763665884</v>
+        <v>0.08840189091372921</v>
       </c>
       <c r="T11">
-        <v>0.9752544488835762</v>
+        <v>0.9838773883078341</v>
       </c>
       <c r="U11">
         <v>0.0518</v>
@@ -2346,7 +2346,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>11.45683348695558</v>
+        <v>10.31115013826003</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2354,22 +2354,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.08360210182235629</v>
+        <v>0.08360775259535304</v>
       </c>
       <c r="C12">
-        <v>879.2637846022749</v>
+        <v>867.9227543310196</v>
       </c>
       <c r="D12">
-        <v>903.173784602275</v>
+        <v>903.0537543310197</v>
       </c>
       <c r="E12">
-        <v>-560.99</v>
+        <v>-549.769</v>
       </c>
       <c r="F12">
-        <v>112.21</v>
+        <v>123.431</v>
       </c>
       <c r="G12">
         <v>88.3</v>
@@ -2390,45 +2390,45 @@
         <v>59.93333333333334</v>
       </c>
       <c r="M12">
-        <v>5.812478</v>
+        <v>6.6035585</v>
       </c>
       <c r="N12">
-        <v>54.12085533333334</v>
+        <v>53.32977483333334</v>
       </c>
       <c r="O12">
-        <v>11.90658817333333</v>
+        <v>11.73255046333333</v>
       </c>
       <c r="P12">
-        <v>42.21426716000001</v>
+        <v>41.59722437000001</v>
       </c>
       <c r="Q12">
-        <v>116.11426716</v>
+        <v>115.49722437</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.08840189091372921</v>
+        <v>0.08878365460152027</v>
       </c>
       <c r="T12">
-        <v>0.9838773883078341</v>
+        <v>0.9926941016517384</v>
       </c>
       <c r="U12">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V12">
         <v>0.22</v>
       </c>
       <c r="W12">
-        <v>0.040404</v>
+        <v>0.04173</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y12">
-        <v>10.31115013826002</v>
+        <v>9.075914650159204</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2436,22 +2436,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.08360775259535304</v>
+        <v>0.08348080336834979</v>
       </c>
       <c r="C13">
-        <v>867.9227543310196</v>
+        <v>859.4060480876947</v>
       </c>
       <c r="D13">
-        <v>903.0537543310197</v>
+        <v>905.7580480876948</v>
       </c>
       <c r="E13">
-        <v>-549.769</v>
+        <v>-538.548</v>
       </c>
       <c r="F13">
-        <v>123.431</v>
+        <v>134.652</v>
       </c>
       <c r="G13">
         <v>88.3</v>
@@ -2472,28 +2472,28 @@
         <v>59.93333333333334</v>
       </c>
       <c r="M13">
-        <v>6.6035585</v>
+        <v>7.203881999999999</v>
       </c>
       <c r="N13">
-        <v>53.32977483333334</v>
+        <v>52.72945133333334</v>
       </c>
       <c r="O13">
-        <v>11.73255046333333</v>
+        <v>11.60047929333333</v>
       </c>
       <c r="P13">
-        <v>41.59722437000001</v>
+        <v>41.12897204</v>
       </c>
       <c r="Q13">
-        <v>115.49722437</v>
+        <v>115.02897204</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.08878365460152027</v>
+        <v>0.08917409473676112</v>
       </c>
       <c r="T13">
-        <v>0.9926941016517384</v>
+        <v>1.001711194844368</v>
       </c>
       <c r="U13">
         <v>0.0535</v>
@@ -2510,7 +2510,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>9.075914650159204</v>
+        <v>8.319588429312605</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2518,22 +2518,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.08348080336834979</v>
+        <v>0.08335385414134654</v>
       </c>
       <c r="C14">
-        <v>859.4060480876947</v>
+        <v>850.9055871025562</v>
       </c>
       <c r="D14">
-        <v>905.7580480876948</v>
+        <v>908.4785871025562</v>
       </c>
       <c r="E14">
-        <v>-538.548</v>
+        <v>-527.327</v>
       </c>
       <c r="F14">
-        <v>134.652</v>
+        <v>145.873</v>
       </c>
       <c r="G14">
         <v>88.3</v>
@@ -2554,28 +2554,28 @@
         <v>59.93333333333334</v>
       </c>
       <c r="M14">
-        <v>7.203881999999999</v>
+        <v>7.804205499999999</v>
       </c>
       <c r="N14">
-        <v>52.72945133333334</v>
+        <v>52.12912783333334</v>
       </c>
       <c r="O14">
-        <v>11.60047929333333</v>
+        <v>11.46840812333333</v>
       </c>
       <c r="P14">
-        <v>41.12897204</v>
+        <v>40.66071971</v>
       </c>
       <c r="Q14">
-        <v>115.02897204</v>
+        <v>114.56071971</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.08917409473676112</v>
+        <v>0.08957351050729487</v>
       </c>
       <c r="T14">
-        <v>1.001711194844368</v>
+        <v>1.010935577535678</v>
       </c>
       <c r="U14">
         <v>0.0535</v>
@@ -2592,7 +2592,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>8.319588429312605</v>
+        <v>7.67962008859625</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2600,22 +2600,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.08335385414134654</v>
+        <v>0.08331426491434327</v>
       </c>
       <c r="C15">
-        <v>850.9055871025562</v>
+        <v>840.5363356422301</v>
       </c>
       <c r="D15">
-        <v>908.4785871025562</v>
+        <v>909.3303356422302</v>
       </c>
       <c r="E15">
-        <v>-527.327</v>
+        <v>-516.106</v>
       </c>
       <c r="F15">
-        <v>145.873</v>
+        <v>157.094</v>
       </c>
       <c r="G15">
         <v>88.3</v>
@@ -2636,45 +2636,45 @@
         <v>59.93333333333334</v>
       </c>
       <c r="M15">
-        <v>7.804205499999999</v>
+        <v>8.5302042</v>
       </c>
       <c r="N15">
-        <v>52.12912783333334</v>
+        <v>51.40312913333334</v>
       </c>
       <c r="O15">
-        <v>11.46840812333333</v>
+        <v>11.30868840933333</v>
       </c>
       <c r="P15">
-        <v>40.66071971</v>
+        <v>40.094440724</v>
       </c>
       <c r="Q15">
-        <v>114.56071971</v>
+        <v>113.994440724</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.08957351050729487</v>
+        <v>0.08998221501667822</v>
       </c>
       <c r="T15">
-        <v>1.010935577535678</v>
+        <v>1.020374480754694</v>
       </c>
       <c r="U15">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V15">
         <v>0.22</v>
       </c>
       <c r="W15">
-        <v>0.04173</v>
+        <v>0.042354</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y15">
-        <v>7.67962008859625</v>
+        <v>7.026013906365025</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2682,22 +2682,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.08331426491434327</v>
+        <v>0.08319355568734003</v>
       </c>
       <c r="C16">
-        <v>840.5363356422301</v>
+        <v>831.9222400115293</v>
       </c>
       <c r="D16">
-        <v>909.3303356422302</v>
+        <v>911.9372400115293</v>
       </c>
       <c r="E16">
-        <v>-516.106</v>
+        <v>-504.885</v>
       </c>
       <c r="F16">
-        <v>157.094</v>
+        <v>168.315</v>
       </c>
       <c r="G16">
         <v>88.3</v>
@@ -2718,28 +2718,28 @@
         <v>59.93333333333334</v>
       </c>
       <c r="M16">
-        <v>8.5302042</v>
+        <v>9.139504499999999</v>
       </c>
       <c r="N16">
-        <v>51.40312913333334</v>
+        <v>50.79382883333334</v>
       </c>
       <c r="O16">
-        <v>11.30868840933333</v>
+        <v>11.17464234333333</v>
       </c>
       <c r="P16">
-        <v>40.094440724</v>
+        <v>39.61918649</v>
       </c>
       <c r="Q16">
-        <v>113.994440724</v>
+        <v>113.51918649</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.08998221501667822</v>
+        <v>0.09040053610275298</v>
       </c>
       <c r="T16">
-        <v>1.020374480754694</v>
+        <v>1.030035475814156</v>
       </c>
       <c r="U16">
         <v>0.0543</v>
@@ -2756,7 +2756,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>7.026013906365025</v>
+        <v>6.557612979274023</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2764,22 +2764,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.08319355568734003</v>
+        <v>0.08307284646033676</v>
       </c>
       <c r="C17">
-        <v>831.9222400115293</v>
+        <v>823.3231345093652</v>
       </c>
       <c r="D17">
-        <v>911.9372400115293</v>
+        <v>914.5591345093652</v>
       </c>
       <c r="E17">
-        <v>-504.8850000000001</v>
+        <v>-493.664</v>
       </c>
       <c r="F17">
-        <v>168.315</v>
+        <v>179.536</v>
       </c>
       <c r="G17">
         <v>88.3</v>
@@ -2800,28 +2800,28 @@
         <v>59.93333333333334</v>
       </c>
       <c r="M17">
-        <v>9.139504499999999</v>
+        <v>9.7488048</v>
       </c>
       <c r="N17">
-        <v>50.79382883333334</v>
+        <v>50.18452853333334</v>
       </c>
       <c r="O17">
-        <v>11.17464234333333</v>
+        <v>11.04059627733333</v>
       </c>
       <c r="P17">
-        <v>39.61918649</v>
+        <v>39.143932256</v>
       </c>
       <c r="Q17">
-        <v>113.51918649</v>
+        <v>113.043932256</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.09040053610275298</v>
+        <v>0.09082881721468662</v>
       </c>
       <c r="T17">
-        <v>1.030035475814156</v>
+        <v>1.039926494565511</v>
       </c>
       <c r="U17">
         <v>0.0543</v>
@@ -2838,7 +2838,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>6.557612979274023</v>
+        <v>6.147762168069396</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2846,22 +2846,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.08307284646033676</v>
+        <v>0.08308473723333351</v>
       </c>
       <c r="C18">
-        <v>823.3231345093652</v>
+        <v>811.8431888174534</v>
       </c>
       <c r="D18">
-        <v>914.5591345093652</v>
+        <v>914.3001888174535</v>
       </c>
       <c r="E18">
-        <v>-493.664</v>
+        <v>-482.443</v>
       </c>
       <c r="F18">
-        <v>179.536</v>
+        <v>190.757</v>
       </c>
       <c r="G18">
         <v>88.3</v>
@@ -2882,45 +2882,45 @@
         <v>59.93333333333334</v>
       </c>
       <c r="M18">
-        <v>9.7488048</v>
+        <v>10.5488621</v>
       </c>
       <c r="N18">
-        <v>50.18452853333334</v>
+        <v>49.38447123333334</v>
       </c>
       <c r="O18">
-        <v>11.04059627733333</v>
+        <v>10.86458367133333</v>
       </c>
       <c r="P18">
-        <v>39.143932256</v>
+        <v>38.519887562</v>
       </c>
       <c r="Q18">
-        <v>113.043932256</v>
+        <v>112.419887562</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.09082881721468662</v>
+        <v>0.09126741835341387</v>
       </c>
       <c r="T18">
-        <v>1.039926494565511</v>
+        <v>1.050055851118103</v>
       </c>
       <c r="U18">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V18">
         <v>0.22</v>
       </c>
       <c r="W18">
-        <v>0.042354</v>
+        <v>0.04313400000000001</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y18">
-        <v>6.147762168069396</v>
+        <v>5.681497470076259</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2928,22 +2928,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.08308473723333351</v>
+        <v>0.08297182800633024</v>
       </c>
       <c r="C19">
-        <v>811.8431888174534</v>
+        <v>803.0869465823382</v>
       </c>
       <c r="D19">
-        <v>914.3001888174535</v>
+        <v>916.7649465823382</v>
       </c>
       <c r="E19">
-        <v>-482.443</v>
+        <v>-471.222</v>
       </c>
       <c r="F19">
-        <v>190.757</v>
+        <v>201.978</v>
       </c>
       <c r="G19">
         <v>88.3</v>
@@ -2964,28 +2964,28 @@
         <v>59.93333333333334</v>
       </c>
       <c r="M19">
-        <v>10.5488621</v>
+        <v>11.1693834</v>
       </c>
       <c r="N19">
-        <v>49.38447123333334</v>
+        <v>48.76394993333334</v>
       </c>
       <c r="O19">
-        <v>10.86458367133333</v>
+        <v>10.72806898533333</v>
       </c>
       <c r="P19">
-        <v>38.519887562</v>
+        <v>38.035880948</v>
       </c>
       <c r="Q19">
-        <v>112.419887562</v>
+        <v>111.935880948</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.09126741835341387</v>
+        <v>0.09171671708089055</v>
       </c>
       <c r="T19">
-        <v>1.050055851118103</v>
+        <v>1.060432265147588</v>
       </c>
       <c r="U19">
         <v>0.0553</v>
@@ -3002,7 +3002,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>5.681497470076259</v>
+        <v>5.365858721738689</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -3010,22 +3010,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.08297182800633025</v>
+        <v>0.08285891877932701</v>
       </c>
       <c r="C20">
-        <v>803.0869465823379</v>
+        <v>794.3440291877199</v>
       </c>
       <c r="D20">
-        <v>916.7649465823379</v>
+        <v>919.2430291877199</v>
       </c>
       <c r="E20">
-        <v>-471.2220000000001</v>
+        <v>-460.0010000000001</v>
       </c>
       <c r="F20">
-        <v>201.978</v>
+        <v>213.199</v>
       </c>
       <c r="G20">
         <v>88.3</v>
@@ -3046,28 +3046,28 @@
         <v>59.93333333333334</v>
       </c>
       <c r="M20">
-        <v>11.1693834</v>
+        <v>11.7899047</v>
       </c>
       <c r="N20">
-        <v>48.76394993333334</v>
+        <v>48.14342863333334</v>
       </c>
       <c r="O20">
-        <v>10.72806898533333</v>
+        <v>10.59155429933333</v>
       </c>
       <c r="P20">
-        <v>38.035880948</v>
+        <v>37.551874334</v>
       </c>
       <c r="Q20">
-        <v>111.935880948</v>
+        <v>111.451874334</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.09171671708089055</v>
+        <v>0.09217710960410741</v>
       </c>
       <c r="T20">
-        <v>1.060432265147588</v>
+        <v>1.071064886930887</v>
       </c>
       <c r="U20">
         <v>0.0553</v>
@@ -3084,7 +3084,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>5.365858721738689</v>
+        <v>5.083445104805074</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3092,22 +3092,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.08285891877932701</v>
+        <v>0.08274600955232375</v>
       </c>
       <c r="C21">
-        <v>794.3440291877199</v>
+        <v>785.6145449805209</v>
       </c>
       <c r="D21">
-        <v>919.2430291877199</v>
+        <v>921.7345449805209</v>
       </c>
       <c r="E21">
-        <v>-460.0010000000001</v>
+        <v>-448.7800000000001</v>
       </c>
       <c r="F21">
-        <v>213.199</v>
+        <v>224.42</v>
       </c>
       <c r="G21">
         <v>88.3</v>
@@ -3128,28 +3128,28 @@
         <v>59.93333333333334</v>
       </c>
       <c r="M21">
-        <v>11.7899047</v>
+        <v>12.410426</v>
       </c>
       <c r="N21">
-        <v>48.14342863333334</v>
+        <v>47.52290733333334</v>
       </c>
       <c r="O21">
-        <v>10.59155429933333</v>
+        <v>10.45503961333333</v>
       </c>
       <c r="P21">
-        <v>37.551874334</v>
+        <v>37.06786772</v>
       </c>
       <c r="Q21">
-        <v>111.451874334</v>
+        <v>110.96786772</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.09217710960410741</v>
+        <v>0.09264901194040467</v>
       </c>
       <c r="T21">
-        <v>1.071064886930887</v>
+        <v>1.081963324258769</v>
       </c>
       <c r="U21">
         <v>0.0553</v>
@@ -3166,7 +3166,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>5.083445104805074</v>
+        <v>4.829272849564821</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3174,22 +3174,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.08274600955232375</v>
+        <v>0.08263310032532051</v>
       </c>
       <c r="C22">
-        <v>785.6145449805209</v>
+        <v>776.8986034855071</v>
       </c>
       <c r="D22">
-        <v>921.7345449805209</v>
+        <v>924.2396034855071</v>
       </c>
       <c r="E22">
-        <v>-448.7800000000001</v>
+        <v>-437.5590000000001</v>
       </c>
       <c r="F22">
-        <v>224.42</v>
+        <v>235.641</v>
       </c>
       <c r="G22">
         <v>88.3</v>
@@ -3210,28 +3210,28 @@
         <v>59.93333333333334</v>
       </c>
       <c r="M22">
-        <v>12.410426</v>
+        <v>13.0309473</v>
       </c>
       <c r="N22">
-        <v>47.52290733333334</v>
+        <v>46.90238603333334</v>
       </c>
       <c r="O22">
-        <v>10.45503961333333</v>
+        <v>10.31852492733333</v>
       </c>
       <c r="P22">
-        <v>37.06786772</v>
+        <v>36.583861106</v>
       </c>
       <c r="Q22">
-        <v>110.96786772</v>
+        <v>110.483861106</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.09264901194040467</v>
+        <v>0.09313286117129177</v>
       </c>
       <c r="T22">
-        <v>1.081963324258769</v>
+        <v>1.093137671392419</v>
       </c>
       <c r="U22">
         <v>0.0553</v>
@@ -3248,7 +3248,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>4.829272849564821</v>
+        <v>4.599307475776019</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3256,22 +3256,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.08263310032532048</v>
+        <v>0.08294919109831723</v>
       </c>
       <c r="C23">
-        <v>776.8986034855078</v>
+        <v>758.6987002006002</v>
       </c>
       <c r="D23">
-        <v>924.2396034855078</v>
+        <v>917.2607002006002</v>
       </c>
       <c r="E23">
-        <v>-437.5590000000001</v>
+        <v>-426.3380000000001</v>
       </c>
       <c r="F23">
-        <v>235.641</v>
+        <v>246.862</v>
       </c>
       <c r="G23">
         <v>88.3</v>
@@ -3292,45 +3292,45 @@
         <v>59.93333333333334</v>
       </c>
       <c r="M23">
-        <v>13.0309473</v>
+        <v>14.2686236</v>
       </c>
       <c r="N23">
-        <v>46.90238603333334</v>
+        <v>45.66470973333334</v>
       </c>
       <c r="O23">
-        <v>10.31852492733334</v>
+        <v>10.04623614133333</v>
       </c>
       <c r="P23">
-        <v>36.58386110600001</v>
+        <v>35.618473592</v>
       </c>
       <c r="Q23">
-        <v>110.483861106</v>
+        <v>109.518473592</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.09313286117129174</v>
+        <v>0.09362911679271439</v>
       </c>
       <c r="T23">
-        <v>1.093137671392419</v>
+        <v>1.104598540247446</v>
       </c>
       <c r="U23">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V23">
         <v>0.22</v>
       </c>
       <c r="W23">
-        <v>0.04313400000000001</v>
+        <v>0.04508400000000001</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y23">
-        <v>4.599307475776021</v>
+        <v>4.200358423732849</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3338,22 +3338,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.08294919109831723</v>
+        <v>0.08285578187131398</v>
       </c>
       <c r="C24">
-        <v>758.6987002006002</v>
+        <v>749.529067964915</v>
       </c>
       <c r="D24">
-        <v>917.2607002006002</v>
+        <v>919.3120679649151</v>
       </c>
       <c r="E24">
-        <v>-426.3380000000001</v>
+        <v>-415.1170000000001</v>
       </c>
       <c r="F24">
-        <v>246.862</v>
+        <v>258.083</v>
       </c>
       <c r="G24">
         <v>88.3</v>
@@ -3374,28 +3374,28 @@
         <v>59.93333333333334</v>
       </c>
       <c r="M24">
-        <v>14.2686236</v>
+        <v>14.9171974</v>
       </c>
       <c r="N24">
-        <v>45.66470973333334</v>
+        <v>45.01613593333334</v>
       </c>
       <c r="O24">
-        <v>10.04623614133333</v>
+        <v>9.903549905333334</v>
       </c>
       <c r="P24">
-        <v>35.618473592</v>
+        <v>35.112586028</v>
       </c>
       <c r="Q24">
-        <v>109.518473592</v>
+        <v>109.012586028</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.09362911679271439</v>
+        <v>0.09413826217053764</v>
       </c>
       <c r="T24">
-        <v>1.104598540247446</v>
+        <v>1.116357094007798</v>
       </c>
       <c r="U24">
         <v>0.0578</v>
@@ -3412,7 +3412,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>4.200358423732849</v>
+        <v>4.017734144440118</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3420,22 +3420,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.08285578187131398</v>
+        <v>0.08341757264431073</v>
       </c>
       <c r="C25">
-        <v>749.529067964915</v>
+        <v>726.1070512605045</v>
       </c>
       <c r="D25">
-        <v>919.3120679649151</v>
+        <v>907.1110512605045</v>
       </c>
       <c r="E25">
-        <v>-415.1170000000001</v>
+        <v>-403.8960000000001</v>
       </c>
       <c r="F25">
-        <v>258.083</v>
+        <v>269.304</v>
       </c>
       <c r="G25">
         <v>88.3</v>
@@ -3456,45 +3456,45 @@
         <v>59.93333333333334</v>
       </c>
       <c r="M25">
-        <v>14.9171974</v>
+        <v>16.5083352</v>
       </c>
       <c r="N25">
-        <v>45.01613593333334</v>
+        <v>43.42499813333334</v>
       </c>
       <c r="O25">
-        <v>9.903549905333334</v>
+        <v>9.553499589333335</v>
       </c>
       <c r="P25">
-        <v>35.112586028</v>
+        <v>33.871498544</v>
       </c>
       <c r="Q25">
-        <v>109.012586028</v>
+        <v>107.771498544</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.09413826217053764</v>
+        <v>0.09466080611093516</v>
       </c>
       <c r="T25">
-        <v>1.116357094007798</v>
+        <v>1.128425083393422</v>
       </c>
       <c r="U25">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V25">
         <v>0.22</v>
       </c>
       <c r="W25">
-        <v>0.04508400000000001</v>
+        <v>0.047814</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y25">
-        <v>4.017734144440118</v>
+        <v>3.630489241176381</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3502,22 +3502,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.08341757264431073</v>
+        <v>0.08389746341730746</v>
       </c>
       <c r="C26">
-        <v>726.1070512605045</v>
+        <v>704.7173523218107</v>
       </c>
       <c r="D26">
-        <v>907.1110512605045</v>
+        <v>896.9423523218107</v>
       </c>
       <c r="E26">
-        <v>-403.8960000000001</v>
+        <v>-392.6750000000001</v>
       </c>
       <c r="F26">
-        <v>269.304</v>
+        <v>280.525</v>
       </c>
       <c r="G26">
         <v>88.3</v>
@@ -3538,45 +3538,45 @@
         <v>59.93333333333334</v>
       </c>
       <c r="M26">
-        <v>16.5083352</v>
+        <v>17.9816525</v>
       </c>
       <c r="N26">
-        <v>43.42499813333334</v>
+        <v>41.95168083333334</v>
       </c>
       <c r="O26">
-        <v>9.553499589333335</v>
+        <v>9.229369783333334</v>
       </c>
       <c r="P26">
-        <v>33.871498544</v>
+        <v>32.72231105000001</v>
       </c>
       <c r="Q26">
-        <v>107.771498544</v>
+        <v>106.62231105</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.09466080611093516</v>
+        <v>0.09519728455640995</v>
       </c>
       <c r="T26">
-        <v>1.128425083393422</v>
+        <v>1.140814885829329</v>
       </c>
       <c r="U26">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V26">
         <v>0.22</v>
       </c>
       <c r="W26">
-        <v>0.047814</v>
+        <v>0.04999800000000001</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y26">
-        <v>3.630489241176381</v>
+        <v>3.333027002570167</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3584,22 +3584,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.08389746341730746</v>
+        <v>0.08385319419030422</v>
       </c>
       <c r="C27">
-        <v>704.7173523218107</v>
+        <v>694.4248446937348</v>
       </c>
       <c r="D27">
-        <v>896.9423523218107</v>
+        <v>897.8708446937349</v>
       </c>
       <c r="E27">
-        <v>-392.6750000000001</v>
+        <v>-381.4540000000001</v>
       </c>
       <c r="F27">
-        <v>280.525</v>
+        <v>291.746</v>
       </c>
       <c r="G27">
         <v>88.3</v>
@@ -3620,28 +3620,28 @@
         <v>59.93333333333334</v>
       </c>
       <c r="M27">
-        <v>17.9816525</v>
+        <v>18.7009186</v>
       </c>
       <c r="N27">
-        <v>41.95168083333334</v>
+        <v>41.23241473333334</v>
       </c>
       <c r="O27">
-        <v>9.229369783333334</v>
+        <v>9.071131241333333</v>
       </c>
       <c r="P27">
-        <v>32.72231105000001</v>
+        <v>32.161283492</v>
       </c>
       <c r="Q27">
-        <v>106.62231105</v>
+        <v>106.061283492</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.09519728455640995</v>
+        <v>0.09574826241933002</v>
       </c>
       <c r="T27">
-        <v>1.140814885829329</v>
+        <v>1.153539547790531</v>
       </c>
       <c r="U27">
         <v>0.0641</v>
@@ -3658,7 +3658,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>3.333027002570167</v>
+        <v>3.204833656317467</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3666,22 +3666,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.08385319419030422</v>
+        <v>0.08380892496330096</v>
       </c>
       <c r="C28">
-        <v>694.4248446937348</v>
+        <v>684.1342613619751</v>
       </c>
       <c r="D28">
-        <v>897.8708446937349</v>
+        <v>898.8012613619751</v>
       </c>
       <c r="E28">
-        <v>-381.4540000000001</v>
+        <v>-370.2330000000001</v>
       </c>
       <c r="F28">
-        <v>291.746</v>
+        <v>302.967</v>
       </c>
       <c r="G28">
         <v>88.3</v>
@@ -3702,28 +3702,28 @@
         <v>59.93333333333334</v>
       </c>
       <c r="M28">
-        <v>18.7009186</v>
+        <v>19.4201847</v>
       </c>
       <c r="N28">
-        <v>41.23241473333334</v>
+        <v>40.51314863333334</v>
       </c>
       <c r="O28">
-        <v>9.071131241333333</v>
+        <v>8.912892699333334</v>
       </c>
       <c r="P28">
-        <v>32.161283492</v>
+        <v>31.600255934</v>
       </c>
       <c r="Q28">
-        <v>106.061283492</v>
+        <v>105.500255934</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.09574826241933002</v>
+        <v>0.09631433556616568</v>
       </c>
       <c r="T28">
-        <v>1.153539547790531</v>
+        <v>1.166612830627383</v>
       </c>
       <c r="U28">
         <v>0.0641</v>
@@ -3740,7 +3740,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>3.204833656317467</v>
+        <v>3.086136113490895</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3748,22 +3748,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.08380892496330096</v>
+        <v>0.0854681757362977</v>
       </c>
       <c r="C29">
-        <v>684.1342613619751</v>
+        <v>639.309420568253</v>
       </c>
       <c r="D29">
-        <v>898.8012613619751</v>
+        <v>865.1974205682531</v>
       </c>
       <c r="E29">
-        <v>-370.2330000000001</v>
+        <v>-359.0120000000001</v>
       </c>
       <c r="F29">
-        <v>302.967</v>
+        <v>314.188</v>
       </c>
       <c r="G29">
         <v>88.3</v>
@@ -3784,45 +3784,45 @@
         <v>59.93333333333334</v>
       </c>
       <c r="M29">
-        <v>19.4201847</v>
+        <v>22.5901172</v>
       </c>
       <c r="N29">
-        <v>40.51314863333334</v>
+        <v>37.34321613333334</v>
       </c>
       <c r="O29">
-        <v>8.912892699333334</v>
+        <v>8.215507549333333</v>
       </c>
       <c r="P29">
-        <v>31.600255934</v>
+        <v>29.127708584</v>
       </c>
       <c r="Q29">
-        <v>105.500255934</v>
+        <v>103.027708584</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.09631433556616568</v>
+        <v>0.09689613296708013</v>
       </c>
       <c r="T29">
-        <v>1.166612830627383</v>
+        <v>1.180049260209703</v>
       </c>
       <c r="U29">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V29">
         <v>0.22</v>
       </c>
       <c r="W29">
-        <v>0.04999800000000001</v>
+        <v>0.05608200000000001</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y29">
-        <v>3.086136113490895</v>
+        <v>2.653077573822119</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3830,22 +3830,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.0854681757362977</v>
+        <v>0.08548474650929444</v>
       </c>
       <c r="C30">
-        <v>639.309420568253</v>
+        <v>627.7654900629858</v>
       </c>
       <c r="D30">
-        <v>865.1974205682531</v>
+        <v>864.8744900629858</v>
       </c>
       <c r="E30">
-        <v>-359.0120000000001</v>
+        <v>-347.7910000000001</v>
       </c>
       <c r="F30">
-        <v>314.188</v>
+        <v>325.409</v>
       </c>
       <c r="G30">
         <v>88.3</v>
@@ -3866,28 +3866,28 @@
         <v>59.93333333333334</v>
       </c>
       <c r="M30">
-        <v>22.5901172</v>
+        <v>23.3969071</v>
       </c>
       <c r="N30">
-        <v>37.34321613333334</v>
+        <v>36.53642623333334</v>
       </c>
       <c r="O30">
-        <v>8.215507549333333</v>
+        <v>8.038013771333334</v>
       </c>
       <c r="P30">
-        <v>29.127708584</v>
+        <v>28.498412462</v>
       </c>
       <c r="Q30">
-        <v>103.027708584</v>
+        <v>102.398412462</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.09689613296708013</v>
+        <v>0.09749431902717526</v>
       </c>
       <c r="T30">
-        <v>1.180049260209703</v>
+        <v>1.193864180766173</v>
       </c>
       <c r="U30">
         <v>0.07190000000000001</v>
@@ -3904,7 +3904,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>2.653077573822119</v>
+        <v>2.561592140242047</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3912,22 +3912,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.08548474650929444</v>
+        <v>0.0864139172822912</v>
       </c>
       <c r="C31">
-        <v>627.7654900629859</v>
+        <v>598.8146746596094</v>
       </c>
       <c r="D31">
-        <v>864.8744900629858</v>
+        <v>847.1446746596093</v>
       </c>
       <c r="E31">
-        <v>-347.7910000000001</v>
+        <v>-336.5700000000001</v>
       </c>
       <c r="F31">
-        <v>325.4089999999999</v>
+        <v>336.6299999999999</v>
       </c>
       <c r="G31">
         <v>88.3</v>
@@ -3948,45 +3948,45 @@
         <v>59.93333333333334</v>
       </c>
       <c r="M31">
-        <v>23.3969071</v>
+        <v>25.516554</v>
       </c>
       <c r="N31">
-        <v>36.53642623333334</v>
+        <v>34.41677933333334</v>
       </c>
       <c r="O31">
-        <v>8.038013771333336</v>
+        <v>7.571691453333334</v>
       </c>
       <c r="P31">
-        <v>28.49841246200001</v>
+        <v>26.84508788</v>
       </c>
       <c r="Q31">
-        <v>102.398412462</v>
+        <v>100.74508788</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.09749431902717526</v>
+        <v>0.09810959611755884</v>
       </c>
       <c r="T31">
-        <v>1.193864180766173</v>
+        <v>1.208073813338541</v>
       </c>
       <c r="U31">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V31">
         <v>0.22</v>
       </c>
       <c r="W31">
-        <v>0.05608200000000001</v>
+        <v>0.05912400000000001</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y31">
-        <v>2.561592140242047</v>
+        <v>2.348802010386408</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3994,22 +3994,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.0864139172822912</v>
+        <v>0.08646090805528793</v>
       </c>
       <c r="C32">
-        <v>598.8146746596094</v>
+        <v>586.7163188735415</v>
       </c>
       <c r="D32">
-        <v>847.1446746596093</v>
+        <v>846.2673188735414</v>
       </c>
       <c r="E32">
-        <v>-336.5700000000001</v>
+        <v>-325.3490000000001</v>
       </c>
       <c r="F32">
-        <v>336.6299999999999</v>
+        <v>347.8509999999999</v>
       </c>
       <c r="G32">
         <v>88.3</v>
@@ -4030,28 +4030,28 @@
         <v>59.93333333333334</v>
       </c>
       <c r="M32">
-        <v>25.516554</v>
+        <v>26.3671058</v>
       </c>
       <c r="N32">
-        <v>34.41677933333334</v>
+        <v>33.56622753333334</v>
       </c>
       <c r="O32">
-        <v>7.571691453333334</v>
+        <v>7.384570057333335</v>
       </c>
       <c r="P32">
-        <v>26.84508788</v>
+        <v>26.18165747600001</v>
       </c>
       <c r="Q32">
-        <v>100.74508788</v>
+        <v>100.081657476</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.09810959611755884</v>
+        <v>0.09874270732650425</v>
       </c>
       <c r="T32">
-        <v>1.208073813338541</v>
+        <v>1.222695319318805</v>
       </c>
       <c r="U32">
         <v>0.07580000000000001</v>
@@ -4068,7 +4068,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>2.348802010386408</v>
+        <v>2.27303420359975</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4076,22 +4076,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.08646090805528793</v>
+        <v>0.08650789882828468</v>
       </c>
       <c r="C33">
-        <v>586.7163188735415</v>
+        <v>574.6197784959124</v>
       </c>
       <c r="D33">
-        <v>846.2673188735414</v>
+        <v>845.3917784959125</v>
       </c>
       <c r="E33">
-        <v>-325.3490000000001</v>
+        <v>-314.128</v>
       </c>
       <c r="F33">
-        <v>347.8509999999999</v>
+        <v>359.072</v>
       </c>
       <c r="G33">
         <v>88.3</v>
@@ -4112,28 +4112,28 @@
         <v>59.93333333333334</v>
       </c>
       <c r="M33">
-        <v>26.3671058</v>
+        <v>27.2176576</v>
       </c>
       <c r="N33">
-        <v>33.56622753333334</v>
+        <v>32.71567573333333</v>
       </c>
       <c r="O33">
-        <v>7.384570057333335</v>
+        <v>7.197448661333333</v>
       </c>
       <c r="P33">
-        <v>26.18165747600001</v>
+        <v>25.518227072</v>
       </c>
       <c r="Q33">
-        <v>100.081657476</v>
+        <v>99.41822707200001</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.09874270732650425</v>
+        <v>0.09939443945335982</v>
       </c>
       <c r="T33">
-        <v>1.222695319318805</v>
+        <v>1.237746869592605</v>
       </c>
       <c r="U33">
         <v>0.07580000000000001</v>
@@ -4150,7 +4150,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>2.27303420359975</v>
+        <v>2.202001884737257</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4158,22 +4158,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.08650789882828468</v>
+        <v>0.08655488960128141</v>
       </c>
       <c r="C34">
-        <v>574.6197784959124</v>
+        <v>562.5250478979318</v>
       </c>
       <c r="D34">
-        <v>845.3917784959125</v>
+        <v>844.5180478979319</v>
       </c>
       <c r="E34">
-        <v>-314.128</v>
+        <v>-302.907</v>
       </c>
       <c r="F34">
-        <v>359.072</v>
+        <v>370.293</v>
       </c>
       <c r="G34">
         <v>88.3</v>
@@ -4194,28 +4194,28 @@
         <v>59.93333333333334</v>
       </c>
       <c r="M34">
-        <v>27.2176576</v>
+        <v>28.0682094</v>
       </c>
       <c r="N34">
-        <v>32.71567573333333</v>
+        <v>31.86512393333333</v>
       </c>
       <c r="O34">
-        <v>7.197448661333333</v>
+        <v>7.010327265333333</v>
       </c>
       <c r="P34">
-        <v>25.518227072</v>
+        <v>24.854796668</v>
       </c>
       <c r="Q34">
-        <v>99.41822707200001</v>
+        <v>98.75479666800001</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.09939443945335982</v>
+        <v>0.1000656262705693</v>
       </c>
       <c r="T34">
-        <v>1.237746869592605</v>
+        <v>1.253247719874579</v>
       </c>
       <c r="U34">
         <v>0.07580000000000001</v>
@@ -4232,7 +4232,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>2.202001884737257</v>
+        <v>2.135274554896734</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4240,22 +4240,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.08655488960128141</v>
+        <v>0.08660188037427817</v>
       </c>
       <c r="C35">
-        <v>562.5250478979318</v>
+        <v>550.4321214740536</v>
       </c>
       <c r="D35">
-        <v>844.5180478979319</v>
+        <v>843.6461214740536</v>
       </c>
       <c r="E35">
-        <v>-302.907</v>
+        <v>-291.686</v>
       </c>
       <c r="F35">
-        <v>370.293</v>
+        <v>381.514</v>
       </c>
       <c r="G35">
         <v>88.3</v>
@@ -4276,28 +4276,28 @@
         <v>59.93333333333334</v>
       </c>
       <c r="M35">
-        <v>28.0682094</v>
+        <v>28.9187612</v>
       </c>
       <c r="N35">
-        <v>31.86512393333333</v>
+        <v>31.01457213333333</v>
       </c>
       <c r="O35">
-        <v>7.010327265333333</v>
+        <v>6.823205869333334</v>
       </c>
       <c r="P35">
-        <v>24.854796668</v>
+        <v>24.191366264</v>
       </c>
       <c r="Q35">
-        <v>98.75479666800001</v>
+        <v>98.09136626400002</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1000656262705693</v>
+        <v>0.1007571520822396</v>
       </c>
       <c r="T35">
-        <v>1.253247719874579</v>
+        <v>1.269218292892371</v>
       </c>
       <c r="U35">
         <v>0.07580000000000001</v>
@@ -4314,7 +4314,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>2.135274554896734</v>
+        <v>2.072472362105654</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4322,22 +4322,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.08660188037427817</v>
+        <v>0.0866488711472749</v>
       </c>
       <c r="C36">
-        <v>550.4321214740536</v>
+        <v>538.3409936418597</v>
       </c>
       <c r="D36">
-        <v>843.6461214740536</v>
+        <v>842.7759936418597</v>
       </c>
       <c r="E36">
-        <v>-291.686</v>
+        <v>-280.465</v>
       </c>
       <c r="F36">
-        <v>381.514</v>
+        <v>392.735</v>
       </c>
       <c r="G36">
         <v>88.3</v>
@@ -4358,28 +4358,28 @@
         <v>59.93333333333334</v>
       </c>
       <c r="M36">
-        <v>28.9187612</v>
+        <v>29.769313</v>
       </c>
       <c r="N36">
-        <v>31.01457213333333</v>
+        <v>30.16402033333333</v>
       </c>
       <c r="O36">
-        <v>6.823205869333334</v>
+        <v>6.636084473333334</v>
       </c>
       <c r="P36">
-        <v>24.191366264</v>
+        <v>23.52793586</v>
       </c>
       <c r="Q36">
-        <v>98.09136626400002</v>
+        <v>97.42793586000001</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1007571520822396</v>
+        <v>0.1014699556111922</v>
       </c>
       <c r="T36">
-        <v>1.269218292892371</v>
+        <v>1.285680268156863</v>
       </c>
       <c r="U36">
         <v>0.07580000000000001</v>
@@ -4396,7 +4396,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>2.072472362105654</v>
+        <v>2.013258866045492</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4404,22 +4404,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.0866488711472749</v>
+        <v>0.09068322192027164</v>
       </c>
       <c r="C37">
-        <v>538.3409936418597</v>
+        <v>458.563598448899</v>
       </c>
       <c r="D37">
-        <v>842.7759936418597</v>
+        <v>774.2195984488991</v>
       </c>
       <c r="E37">
-        <v>-280.465</v>
+        <v>-269.244</v>
       </c>
       <c r="F37">
-        <v>392.735</v>
+        <v>403.956</v>
       </c>
       <c r="G37">
         <v>88.3</v>
@@ -4440,45 +4440,45 @@
         <v>59.93333333333334</v>
       </c>
       <c r="M37">
-        <v>29.769313</v>
+        <v>36.35604</v>
       </c>
       <c r="N37">
-        <v>30.16402033333333</v>
+        <v>23.57729333333334</v>
       </c>
       <c r="O37">
-        <v>6.636084473333334</v>
+        <v>5.187004533333334</v>
       </c>
       <c r="P37">
-        <v>23.52793586</v>
+        <v>18.3902888</v>
       </c>
       <c r="Q37">
-        <v>97.42793586000001</v>
+        <v>92.29028880000001</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1014699556111922</v>
+        <v>0.1022050342504245</v>
       </c>
       <c r="T37">
-        <v>1.285680268156863</v>
+        <v>1.302656680148371</v>
       </c>
       <c r="U37">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V37">
         <v>0.22</v>
       </c>
       <c r="W37">
-        <v>0.05912400000000001</v>
+        <v>0.0702</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y37">
-        <v>2.013258866045492</v>
+        <v>1.648511040623053</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4486,22 +4486,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.09068322192027166</v>
+        <v>0.09084097269326839</v>
       </c>
       <c r="C38">
-        <v>458.5635984488989</v>
+        <v>444.8877843146635</v>
       </c>
       <c r="D38">
-        <v>774.2195984488989</v>
+        <v>771.7647843146635</v>
       </c>
       <c r="E38">
-        <v>-269.2440000000001</v>
+        <v>-258.0230000000001</v>
       </c>
       <c r="F38">
-        <v>403.956</v>
+        <v>415.177</v>
       </c>
       <c r="G38">
         <v>88.3</v>
@@ -4522,28 +4522,28 @@
         <v>59.93333333333334</v>
       </c>
       <c r="M38">
-        <v>36.35603999999999</v>
+        <v>37.36593</v>
       </c>
       <c r="N38">
-        <v>23.57729333333334</v>
+        <v>22.56740333333334</v>
       </c>
       <c r="O38">
-        <v>5.187004533333336</v>
+        <v>4.964828733333334</v>
       </c>
       <c r="P38">
-        <v>18.39028880000001</v>
+        <v>17.6025746</v>
       </c>
       <c r="Q38">
-        <v>92.29028880000001</v>
+        <v>91.5025746</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1022050342504245</v>
+        <v>0.1029634487194736</v>
       </c>
       <c r="T38">
-        <v>1.302656680148371</v>
+        <v>1.320172025853895</v>
       </c>
       <c r="U38">
         <v>0.09</v>
@@ -4560,7 +4560,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>1.648511040623053</v>
+        <v>1.603956688173781</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4568,22 +4568,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.09084097269326839</v>
+        <v>0.09099872346626514</v>
       </c>
       <c r="C39">
-        <v>444.8877843146635</v>
+        <v>431.2274879117603</v>
       </c>
       <c r="D39">
-        <v>771.7647843146635</v>
+        <v>769.3254879117603</v>
       </c>
       <c r="E39">
-        <v>-258.0230000000001</v>
+        <v>-246.8020000000001</v>
       </c>
       <c r="F39">
-        <v>415.177</v>
+        <v>426.398</v>
       </c>
       <c r="G39">
         <v>88.3</v>
@@ -4604,28 +4604,28 @@
         <v>59.93333333333334</v>
       </c>
       <c r="M39">
-        <v>37.36593</v>
+        <v>38.37582</v>
       </c>
       <c r="N39">
-        <v>22.56740333333334</v>
+        <v>21.55751333333334</v>
       </c>
       <c r="O39">
-        <v>4.964828733333334</v>
+        <v>4.742652933333335</v>
       </c>
       <c r="P39">
-        <v>17.6025746</v>
+        <v>16.8148604</v>
       </c>
       <c r="Q39">
-        <v>91.5025746</v>
+        <v>90.71486040000001</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1029634487194736</v>
+        <v>0.1037463281713954</v>
       </c>
       <c r="T39">
-        <v>1.320172025853895</v>
+        <v>1.33825238271121</v>
       </c>
       <c r="U39">
         <v>0.09</v>
@@ -4642,7 +4642,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>1.603956688173781</v>
+        <v>1.561747301642892</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4650,22 +4650,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.09099872346626514</v>
+        <v>0.09115647423926189</v>
       </c>
       <c r="C40">
-        <v>431.2274879117603</v>
+        <v>417.5825625643436</v>
       </c>
       <c r="D40">
-        <v>769.3254879117603</v>
+        <v>766.9015625643436</v>
       </c>
       <c r="E40">
-        <v>-246.8020000000001</v>
+        <v>-235.5810000000001</v>
       </c>
       <c r="F40">
-        <v>426.398</v>
+        <v>437.619</v>
       </c>
       <c r="G40">
         <v>88.3</v>
@@ -4686,28 +4686,28 @@
         <v>59.93333333333334</v>
       </c>
       <c r="M40">
-        <v>38.37582</v>
+        <v>39.38571</v>
       </c>
       <c r="N40">
-        <v>21.55751333333334</v>
+        <v>20.54762333333334</v>
       </c>
       <c r="O40">
-        <v>4.742652933333335</v>
+        <v>4.520477133333335</v>
       </c>
       <c r="P40">
-        <v>16.8148604</v>
+        <v>16.0271462</v>
       </c>
       <c r="Q40">
-        <v>90.71486040000001</v>
+        <v>89.92714620000001</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1037463281713954</v>
+        <v>0.1045548758020687</v>
       </c>
       <c r="T40">
-        <v>1.33825238271121</v>
+        <v>1.356925538154011</v>
       </c>
       <c r="U40">
         <v>0.09</v>
@@ -4724,7 +4724,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>1.561747301642892</v>
+        <v>1.521702499036664</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4732,22 +4732,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.09115647423926189</v>
+        <v>0.1105155128335837</v>
       </c>
       <c r="C41">
-        <v>417.5825625643436</v>
+        <v>192.5194535145696</v>
       </c>
       <c r="D41">
-        <v>766.9015625643436</v>
+        <v>553.0594535145697</v>
       </c>
       <c r="E41">
-        <v>-235.5810000000001</v>
+        <v>-224.3600000000001</v>
       </c>
       <c r="F41">
-        <v>437.619</v>
+        <v>448.84</v>
       </c>
       <c r="G41">
         <v>88.3</v>
@@ -4768,45 +4768,45 @@
         <v>59.93333333333334</v>
       </c>
       <c r="M41">
-        <v>39.38571</v>
+        <v>65.889712</v>
       </c>
       <c r="N41">
-        <v>20.54762333333334</v>
+        <v>-5.956378666666666</v>
       </c>
       <c r="O41">
-        <v>4.520477133333335</v>
+        <v>-1.310403306666666</v>
       </c>
       <c r="P41">
-        <v>16.0271462</v>
+        <v>-4.64597536</v>
       </c>
       <c r="Q41">
-        <v>89.92714620000001</v>
+        <v>69.25402464000001</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1045548758020687</v>
+        <v>0.1059101658852413</v>
       </c>
       <c r="T41">
-        <v>1.356925538154011</v>
+        <v>1.388225540074857</v>
       </c>
       <c r="U41">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V41">
-        <v>0.22</v>
+        <v>0.2001121712799918</v>
       </c>
       <c r="W41">
-        <v>0.0702</v>
+        <v>0.1174235332560972</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y41">
-        <v>1.521702499036664</v>
+        <v>0.9096007785454174</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4814,22 +4814,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1105155128335837</v>
+        <v>0.1115255128335837</v>
       </c>
       <c r="C42">
-        <v>192.5194535145696</v>
+        <v>173.3681357596702</v>
       </c>
       <c r="D42">
-        <v>553.0594535145697</v>
+        <v>545.1291357596702</v>
       </c>
       <c r="E42">
-        <v>-224.3600000000001</v>
+        <v>-213.1390000000001</v>
       </c>
       <c r="F42">
-        <v>448.84</v>
+        <v>460.061</v>
       </c>
       <c r="G42">
         <v>88.3</v>
@@ -4850,37 +4850,37 @@
         <v>59.93333333333334</v>
       </c>
       <c r="M42">
-        <v>65.889712</v>
+        <v>67.5369548</v>
       </c>
       <c r="N42">
-        <v>-5.956378666666666</v>
+        <v>-7.603621466666667</v>
       </c>
       <c r="O42">
-        <v>-1.310403306666666</v>
+        <v>-1.672796722666667</v>
       </c>
       <c r="P42">
-        <v>-4.64597536</v>
+        <v>-5.930824744</v>
       </c>
       <c r="Q42">
-        <v>69.25402464000001</v>
+        <v>67.969175256</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1059101658852413</v>
+        <v>0.1069289822561776</v>
       </c>
       <c r="T42">
-        <v>1.388225540074857</v>
+        <v>1.411754786516804</v>
       </c>
       <c r="U42">
         <v>0.1468</v>
       </c>
       <c r="V42">
-        <v>0.2001121712799918</v>
+        <v>0.1952313866146262</v>
       </c>
       <c r="W42">
-        <v>0.1174235332560972</v>
+        <v>0.1181400324449729</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4888,7 +4888,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.9096007785454174</v>
+        <v>0.8874153937028463</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4896,22 +4896,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1115255128335837</v>
+        <v>0.1125355128335837</v>
       </c>
       <c r="C43">
-        <v>173.3681357596702</v>
+        <v>154.441028651433</v>
       </c>
       <c r="D43">
-        <v>545.1291357596702</v>
+        <v>537.423028651433</v>
       </c>
       <c r="E43">
-        <v>-213.1390000000001</v>
+        <v>-201.9180000000001</v>
       </c>
       <c r="F43">
-        <v>460.061</v>
+        <v>471.282</v>
       </c>
       <c r="G43">
         <v>88.3</v>
@@ -4932,37 +4932,37 @@
         <v>59.93333333333334</v>
       </c>
       <c r="M43">
-        <v>67.5369548</v>
+        <v>69.1841976</v>
       </c>
       <c r="N43">
-        <v>-7.603621466666667</v>
+        <v>-9.250864266666667</v>
       </c>
       <c r="O43">
-        <v>-1.672796722666667</v>
+        <v>-2.035190138666667</v>
       </c>
       <c r="P43">
-        <v>-5.930824744</v>
+        <v>-7.215674128000001</v>
       </c>
       <c r="Q43">
-        <v>67.969175256</v>
+        <v>66.684325872</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1069289822561776</v>
+        <v>0.1079829302261117</v>
       </c>
       <c r="T43">
-        <v>1.411754786516804</v>
+        <v>1.436095386284335</v>
       </c>
       <c r="U43">
         <v>0.1468</v>
       </c>
       <c r="V43">
-        <v>0.1952313866146262</v>
+        <v>0.1905830202666589</v>
       </c>
       <c r="W43">
-        <v>0.1181400324449729</v>
+        <v>0.1188224126248545</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4970,7 +4970,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.8874153937028463</v>
+        <v>0.8662864557575404</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4978,22 +4978,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1125355128335837</v>
+        <v>0.1135455128335837</v>
       </c>
       <c r="C44">
-        <v>154.441028651433</v>
+        <v>135.728756206976</v>
       </c>
       <c r="D44">
-        <v>537.423028651433</v>
+        <v>529.9317562069759</v>
       </c>
       <c r="E44">
-        <v>-201.9180000000001</v>
+        <v>-190.6970000000001</v>
       </c>
       <c r="F44">
-        <v>471.2819999999999</v>
+        <v>482.5029999999999</v>
       </c>
       <c r="G44">
         <v>88.3</v>
@@ -5014,37 +5014,37 @@
         <v>59.93333333333334</v>
       </c>
       <c r="M44">
-        <v>69.18419759999999</v>
+        <v>70.83144039999999</v>
       </c>
       <c r="N44">
-        <v>-9.250864266666653</v>
+        <v>-10.89810706666665</v>
       </c>
       <c r="O44">
-        <v>-2.035190138666664</v>
+        <v>-2.397583554666664</v>
       </c>
       <c r="P44">
-        <v>-7.215674127999989</v>
+        <v>-8.50052351199999</v>
       </c>
       <c r="Q44">
-        <v>66.68432587200002</v>
+        <v>65.39947648800002</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1079829302261117</v>
+        <v>0.1090738588265698</v>
       </c>
       <c r="T44">
-        <v>1.436095386284335</v>
+        <v>1.46129004218406</v>
       </c>
       <c r="U44">
         <v>0.1468</v>
       </c>
       <c r="V44">
-        <v>0.1905830202666589</v>
+        <v>0.1861508570046436</v>
       </c>
       <c r="W44">
-        <v>0.1188224126248545</v>
+        <v>0.1194730541917183</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -5052,7 +5052,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.8662864557575406</v>
+        <v>0.8461402591120164</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5060,22 +5060,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1135455128335837</v>
+        <v>0.1145555128335837</v>
       </c>
       <c r="C45">
-        <v>135.728756206976</v>
+        <v>117.2224580330571</v>
       </c>
       <c r="D45">
-        <v>529.9317562069759</v>
+        <v>522.6464580330571</v>
       </c>
       <c r="E45">
-        <v>-190.6970000000001</v>
+        <v>-179.4760000000001</v>
       </c>
       <c r="F45">
-        <v>482.5029999999999</v>
+        <v>493.724</v>
       </c>
       <c r="G45">
         <v>88.3</v>
@@ -5096,37 +5096,37 @@
         <v>59.93333333333334</v>
       </c>
       <c r="M45">
-        <v>70.83144039999999</v>
+        <v>72.47868320000001</v>
       </c>
       <c r="N45">
-        <v>-10.89810706666665</v>
+        <v>-12.54534986666667</v>
       </c>
       <c r="O45">
-        <v>-2.397583554666664</v>
+        <v>-2.759976970666667</v>
       </c>
       <c r="P45">
-        <v>-8.50052351199999</v>
+        <v>-9.785372896000002</v>
       </c>
       <c r="Q45">
-        <v>65.39947648800002</v>
+        <v>64.11462710400001</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1090738588265698</v>
+        <v>0.1102037491627585</v>
       </c>
       <c r="T45">
-        <v>1.46129004218406</v>
+        <v>1.487384507223061</v>
       </c>
       <c r="U45">
         <v>0.1468</v>
       </c>
       <c r="V45">
-        <v>0.1861508570046436</v>
+        <v>0.1819201557090835</v>
       </c>
       <c r="W45">
-        <v>0.1194730541917183</v>
+        <v>0.1200941211419066</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5134,7 +5134,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.8461402591120164</v>
+        <v>0.8269097986776521</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5142,22 +5142,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1145555128335837</v>
+        <v>0.1155655128335837</v>
       </c>
       <c r="C46">
-        <v>117.2224580330571</v>
+        <v>98.91375436605148</v>
       </c>
       <c r="D46">
-        <v>522.6464580330571</v>
+        <v>515.5587543660515</v>
       </c>
       <c r="E46">
-        <v>-179.4760000000001</v>
+        <v>-168.2550000000001</v>
       </c>
       <c r="F46">
-        <v>493.724</v>
+        <v>504.945</v>
       </c>
       <c r="G46">
         <v>88.3</v>
@@ -5178,37 +5178,37 @@
         <v>59.93333333333334</v>
       </c>
       <c r="M46">
-        <v>72.47868320000001</v>
+        <v>74.12592600000001</v>
       </c>
       <c r="N46">
-        <v>-12.54534986666667</v>
+        <v>-14.19259266666667</v>
       </c>
       <c r="O46">
-        <v>-2.759976970666667</v>
+        <v>-3.122370386666667</v>
       </c>
       <c r="P46">
-        <v>-9.785372896000002</v>
+        <v>-11.07022228</v>
       </c>
       <c r="Q46">
-        <v>64.11462710400001</v>
+        <v>62.82977772</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1102037491627585</v>
+        <v>0.1113747264202632</v>
       </c>
       <c r="T46">
-        <v>1.487384507223061</v>
+        <v>1.514427861899844</v>
       </c>
       <c r="U46">
         <v>0.1468</v>
       </c>
       <c r="V46">
-        <v>0.1819201557090835</v>
+        <v>0.1778774855822149</v>
       </c>
       <c r="W46">
-        <v>0.1200941211419066</v>
+        <v>0.1206875851165309</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5216,7 +5216,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.8269097986776521</v>
+        <v>0.8085340253737043</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5224,22 +5224,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1155655128335837</v>
+        <v>0.1422594227255517</v>
       </c>
       <c r="C47">
-        <v>98.91375436605148</v>
+        <v>-48.33686367705786</v>
       </c>
       <c r="D47">
-        <v>515.5587543660515</v>
+        <v>379.5291363229421</v>
       </c>
       <c r="E47">
-        <v>-168.2550000000001</v>
+        <v>-157.0340000000001</v>
       </c>
       <c r="F47">
-        <v>504.945</v>
+        <v>516.1659999999999</v>
       </c>
       <c r="G47">
         <v>88.3</v>
@@ -5260,45 +5260,45 @@
         <v>59.93333333333334</v>
       </c>
       <c r="M47">
-        <v>74.12592600000001</v>
+        <v>103.6461328</v>
       </c>
       <c r="N47">
-        <v>-14.19259266666667</v>
+        <v>-43.71279946666665</v>
       </c>
       <c r="O47">
-        <v>-3.122370386666667</v>
+        <v>-9.616815882666664</v>
       </c>
       <c r="P47">
-        <v>-11.07022228</v>
+        <v>-34.09598358399999</v>
       </c>
       <c r="Q47">
-        <v>62.82977772</v>
+        <v>39.80401641600002</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1113747264202632</v>
+        <v>0.1141518693020608</v>
       </c>
       <c r="T47">
-        <v>1.514427861899844</v>
+        <v>1.578565110902096</v>
       </c>
       <c r="U47">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V47">
-        <v>0.1778774855822149</v>
+        <v>0.1272149088164854</v>
       </c>
       <c r="W47">
-        <v>0.1206875851165309</v>
+        <v>0.1752552463096498</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y47">
-        <v>0.8085340253737043</v>
+        <v>0.578249585529479</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5306,22 +5306,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1422594227255517</v>
+        <v>0.1438094227255517</v>
       </c>
       <c r="C48">
-        <v>-48.33686367705786</v>
+        <v>-65.28472622629272</v>
       </c>
       <c r="D48">
-        <v>379.5291363229421</v>
+        <v>373.8022737737072</v>
       </c>
       <c r="E48">
-        <v>-157.0340000000001</v>
+        <v>-145.8130000000001</v>
       </c>
       <c r="F48">
-        <v>516.1659999999999</v>
+        <v>527.3869999999999</v>
       </c>
       <c r="G48">
         <v>88.3</v>
@@ -5342,37 +5342,37 @@
         <v>59.93333333333334</v>
       </c>
       <c r="M48">
-        <v>103.6461328</v>
+        <v>105.8993096</v>
       </c>
       <c r="N48">
-        <v>-43.71279946666665</v>
+        <v>-45.96597626666666</v>
       </c>
       <c r="O48">
-        <v>-9.616815882666664</v>
+        <v>-10.11251477866666</v>
       </c>
       <c r="P48">
-        <v>-34.09598358399999</v>
+        <v>-35.85346148799999</v>
       </c>
       <c r="Q48">
-        <v>39.80401641600002</v>
+        <v>38.04653851200001</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1141518693020608</v>
+        <v>0.1154415272134204</v>
       </c>
       <c r="T48">
-        <v>1.578565110902096</v>
+        <v>1.608349358277607</v>
       </c>
       <c r="U48">
         <v>0.2008</v>
       </c>
       <c r="V48">
-        <v>0.1272149088164854</v>
+        <v>0.1245082086289006</v>
       </c>
       <c r="W48">
-        <v>0.1752552463096498</v>
+        <v>0.1757987517073168</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5380,7 +5380,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.578249585529479</v>
+        <v>0.565946402858639</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5388,22 +5388,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1438094227255517</v>
+        <v>0.1453594227255517</v>
       </c>
       <c r="C49">
-        <v>-65.28472622629272</v>
+        <v>-82.06232819682737</v>
       </c>
       <c r="D49">
-        <v>373.8022737737072</v>
+        <v>368.2456718031726</v>
       </c>
       <c r="E49">
-        <v>-145.8130000000001</v>
+        <v>-134.5920000000001</v>
       </c>
       <c r="F49">
-        <v>527.3869999999999</v>
+        <v>538.6079999999999</v>
       </c>
       <c r="G49">
         <v>88.3</v>
@@ -5424,37 +5424,37 @@
         <v>59.93333333333334</v>
       </c>
       <c r="M49">
-        <v>105.8993096</v>
+        <v>108.1524864</v>
       </c>
       <c r="N49">
-        <v>-45.96597626666666</v>
+        <v>-48.21915306666665</v>
       </c>
       <c r="O49">
-        <v>-10.11251477866666</v>
+        <v>-10.60821367466666</v>
       </c>
       <c r="P49">
-        <v>-35.85346148799999</v>
+        <v>-37.61093939199998</v>
       </c>
       <c r="Q49">
-        <v>38.04653851200001</v>
+        <v>36.28906060800002</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1154415272134204</v>
+        <v>0.11678078735214</v>
       </c>
       <c r="T49">
-        <v>1.608349358277607</v>
+        <v>1.6392791536291</v>
       </c>
       <c r="U49">
         <v>0.2008</v>
       </c>
       <c r="V49">
-        <v>0.1245082086289006</v>
+        <v>0.1219142876157985</v>
       </c>
       <c r="W49">
-        <v>0.1757987517073168</v>
+        <v>0.1763196110467477</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.565946402858639</v>
+        <v>0.5541558527990841</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5470,22 +5470,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1453594227255517</v>
+        <v>0.1469094227255517</v>
       </c>
       <c r="C50">
-        <v>-82.06232819682737</v>
+        <v>-98.67715118717666</v>
       </c>
       <c r="D50">
-        <v>368.2456718031726</v>
+        <v>362.8518488128233</v>
       </c>
       <c r="E50">
-        <v>-134.5920000000001</v>
+        <v>-123.3710000000001</v>
       </c>
       <c r="F50">
-        <v>538.6079999999999</v>
+        <v>549.829</v>
       </c>
       <c r="G50">
         <v>88.3</v>
@@ -5506,37 +5506,37 @@
         <v>59.93333333333334</v>
       </c>
       <c r="M50">
-        <v>108.1524864</v>
+        <v>110.4056632</v>
       </c>
       <c r="N50">
-        <v>-48.21915306666665</v>
+        <v>-50.47232986666666</v>
       </c>
       <c r="O50">
-        <v>-10.60821367466666</v>
+        <v>-11.10391257066666</v>
       </c>
       <c r="P50">
-        <v>-37.61093939199998</v>
+        <v>-39.36841729599999</v>
       </c>
       <c r="Q50">
-        <v>36.28906060800002</v>
+        <v>34.53158270400002</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.11678078735214</v>
+        <v>0.1181725674962996</v>
       </c>
       <c r="T50">
-        <v>1.6392791536291</v>
+        <v>1.671421882131631</v>
       </c>
       <c r="U50">
         <v>0.2008</v>
       </c>
       <c r="V50">
-        <v>0.1219142876157985</v>
+        <v>0.1194262409297618</v>
       </c>
       <c r="W50">
-        <v>0.1763196110467477</v>
+        <v>0.1768192108213038</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5544,7 +5544,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.5541558527990841</v>
+        <v>0.5428465496807354</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5552,22 +5552,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1469094227255517</v>
+        <v>0.1484594227255517</v>
       </c>
       <c r="C51">
-        <v>-98.67715118717666</v>
+        <v>-115.1362447813749</v>
       </c>
       <c r="D51">
-        <v>362.8518488128233</v>
+        <v>357.613755218625</v>
       </c>
       <c r="E51">
-        <v>-123.3710000000001</v>
+        <v>-112.1500000000001</v>
       </c>
       <c r="F51">
-        <v>549.829</v>
+        <v>561.05</v>
       </c>
       <c r="G51">
         <v>88.3</v>
@@ -5588,37 +5588,37 @@
         <v>59.93333333333334</v>
       </c>
       <c r="M51">
-        <v>110.4056632</v>
+        <v>112.65884</v>
       </c>
       <c r="N51">
-        <v>-50.47232986666666</v>
+        <v>-52.72550666666666</v>
       </c>
       <c r="O51">
-        <v>-11.10391257066666</v>
+        <v>-11.59961146666667</v>
       </c>
       <c r="P51">
-        <v>-39.36841729599999</v>
+        <v>-41.1258952</v>
       </c>
       <c r="Q51">
-        <v>34.53158270400002</v>
+        <v>32.77410480000001</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1181725674962996</v>
+        <v>0.1196200188462256</v>
       </c>
       <c r="T51">
-        <v>1.671421882131631</v>
+        <v>1.704850319774264</v>
       </c>
       <c r="U51">
         <v>0.2008</v>
       </c>
       <c r="V51">
-        <v>0.1194262409297618</v>
+        <v>0.1170377161111665</v>
       </c>
       <c r="W51">
-        <v>0.1768192108213038</v>
+        <v>0.1772988266048778</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5626,7 +5626,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.5428465496807354</v>
+        <v>0.5319896186871207</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5634,22 +5634,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1484594227255517</v>
+        <v>0.1500094227255517</v>
       </c>
       <c r="C52">
-        <v>-115.1362447813749</v>
+        <v>-131.446257287825</v>
       </c>
       <c r="D52">
-        <v>357.613755218625</v>
+        <v>352.5247427121749</v>
       </c>
       <c r="E52">
-        <v>-112.1500000000001</v>
+        <v>-100.9290000000001</v>
       </c>
       <c r="F52">
-        <v>561.05</v>
+        <v>572.271</v>
       </c>
       <c r="G52">
         <v>88.3</v>
@@ -5670,37 +5670,37 @@
         <v>59.93333333333334</v>
       </c>
       <c r="M52">
-        <v>112.65884</v>
+        <v>114.9120168</v>
       </c>
       <c r="N52">
-        <v>-52.72550666666666</v>
+        <v>-54.97868346666665</v>
       </c>
       <c r="O52">
-        <v>-11.59961146666667</v>
+        <v>-12.09531036266666</v>
       </c>
       <c r="P52">
-        <v>-41.1258952</v>
+        <v>-42.88337310399999</v>
       </c>
       <c r="Q52">
-        <v>32.77410480000001</v>
+        <v>31.01662689600002</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1196200188462256</v>
+        <v>0.1211265498430874</v>
       </c>
       <c r="T52">
-        <v>1.704850319774264</v>
+        <v>1.739643183443126</v>
       </c>
       <c r="U52">
         <v>0.2008</v>
       </c>
       <c r="V52">
-        <v>0.1170377161111665</v>
+        <v>0.1147428589325162</v>
       </c>
       <c r="W52">
-        <v>0.1772988266048778</v>
+        <v>0.1777596339263507</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5708,7 +5708,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.5319896186871207</v>
+        <v>0.5215584496932556</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5716,22 +5716,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1500094227255517</v>
+        <v>0.1515594227255517</v>
       </c>
       <c r="C53">
-        <v>-131.446257287825</v>
+        <v>-147.6134638904038</v>
       </c>
       <c r="D53">
-        <v>352.5247427121749</v>
+        <v>347.5785361095962</v>
       </c>
       <c r="E53">
-        <v>-100.9290000000001</v>
+        <v>-89.70800000000008</v>
       </c>
       <c r="F53">
-        <v>572.271</v>
+        <v>583.492</v>
       </c>
       <c r="G53">
         <v>88.3</v>
@@ -5752,37 +5752,37 @@
         <v>59.93333333333334</v>
       </c>
       <c r="M53">
-        <v>114.9120168</v>
+        <v>117.1651936</v>
       </c>
       <c r="N53">
-        <v>-54.97868346666665</v>
+        <v>-57.23186026666666</v>
       </c>
       <c r="O53">
-        <v>-12.09531036266666</v>
+        <v>-12.59100925866666</v>
       </c>
       <c r="P53">
-        <v>-42.88337310399999</v>
+        <v>-44.64085100799999</v>
       </c>
       <c r="Q53">
-        <v>31.01662689600002</v>
+        <v>29.25914899200001</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1211265498430874</v>
+        <v>0.1226958529648184</v>
       </c>
       <c r="T53">
-        <v>1.739643183443126</v>
+        <v>1.775885749764858</v>
       </c>
       <c r="U53">
         <v>0.2008</v>
       </c>
       <c r="V53">
-        <v>0.1147428589325162</v>
+        <v>0.1125362654915063</v>
       </c>
       <c r="W53">
-        <v>0.1777596339263507</v>
+        <v>0.1782027178893055</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5790,7 +5790,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.5215584496932556</v>
+        <v>0.5115284795068469</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5798,22 +5798,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1515594227255517</v>
+        <v>0.1531094227255517</v>
       </c>
       <c r="C54">
-        <v>-147.6134638904038</v>
+        <v>-163.643792462461</v>
       </c>
       <c r="D54">
-        <v>347.5785361095962</v>
+        <v>342.7692075375389</v>
       </c>
       <c r="E54">
-        <v>-89.70800000000008</v>
+        <v>-78.48700000000008</v>
       </c>
       <c r="F54">
-        <v>583.492</v>
+        <v>594.713</v>
       </c>
       <c r="G54">
         <v>88.3</v>
@@ -5834,37 +5834,37 @@
         <v>59.93333333333334</v>
       </c>
       <c r="M54">
-        <v>117.1651936</v>
+        <v>119.4183704</v>
       </c>
       <c r="N54">
-        <v>-57.23186026666666</v>
+        <v>-59.48503706666666</v>
       </c>
       <c r="O54">
-        <v>-12.59100925866666</v>
+        <v>-13.08670815466667</v>
       </c>
       <c r="P54">
-        <v>-44.64085100799999</v>
+        <v>-46.398328912</v>
       </c>
       <c r="Q54">
-        <v>29.25914899200001</v>
+        <v>27.50167108800001</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1226958529648184</v>
+        <v>0.1243319349427932</v>
       </c>
       <c r="T54">
-        <v>1.775885749764858</v>
+        <v>1.813670552951345</v>
       </c>
       <c r="U54">
         <v>0.2008</v>
       </c>
       <c r="V54">
-        <v>0.1125362654915063</v>
+        <v>0.1104129397275156</v>
       </c>
       <c r="W54">
-        <v>0.1782027178893055</v>
+        <v>0.1786290817027149</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5872,7 +5872,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.5115284795068469</v>
+        <v>0.5018769987614347</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5880,22 +5880,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1531094227255517</v>
+        <v>0.1738999505602619</v>
       </c>
       <c r="C55">
-        <v>-163.643792462461</v>
+        <v>-228.5223509184906</v>
       </c>
       <c r="D55">
-        <v>342.7692075375389</v>
+        <v>289.1116490815093</v>
       </c>
       <c r="E55">
-        <v>-78.48700000000008</v>
+        <v>-67.26600000000008</v>
       </c>
       <c r="F55">
-        <v>594.713</v>
+        <v>605.934</v>
       </c>
       <c r="G55">
         <v>88.3</v>
@@ -5916,45 +5916,45 @@
         <v>59.93333333333334</v>
       </c>
       <c r="M55">
-        <v>119.4183704</v>
+        <v>142.8792372</v>
       </c>
       <c r="N55">
-        <v>-59.48503706666666</v>
+        <v>-82.94590386666667</v>
       </c>
       <c r="O55">
-        <v>-13.08670815466667</v>
+        <v>-18.24809885066667</v>
       </c>
       <c r="P55">
-        <v>-46.398328912</v>
+        <v>-64.697805016</v>
       </c>
       <c r="Q55">
-        <v>27.50167108800001</v>
+        <v>9.202194984000002</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1243319349427932</v>
+        <v>0.1267794288213543</v>
       </c>
       <c r="T55">
-        <v>1.813670552951345</v>
+        <v>1.870194661001255</v>
       </c>
       <c r="U55">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V55">
-        <v>0.1104129397275156</v>
+        <v>0.09228306079823706</v>
       </c>
       <c r="W55">
-        <v>0.1786290817027149</v>
+        <v>0.2140396542637757</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y55">
-        <v>0.5018769987614347</v>
+        <v>0.4194684581738048</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5962,22 +5962,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1738999505602619</v>
+        <v>0.1757999505602619</v>
       </c>
       <c r="C56">
-        <v>-228.5223509184906</v>
+        <v>-243.8210371367833</v>
       </c>
       <c r="D56">
-        <v>289.1116490815093</v>
+        <v>285.0339628632167</v>
       </c>
       <c r="E56">
-        <v>-67.26600000000008</v>
+        <v>-56.04500000000007</v>
       </c>
       <c r="F56">
-        <v>605.934</v>
+        <v>617.155</v>
       </c>
       <c r="G56">
         <v>88.3</v>
@@ -5998,37 +5998,37 @@
         <v>59.93333333333334</v>
       </c>
       <c r="M56">
-        <v>142.8792372</v>
+        <v>145.525149</v>
       </c>
       <c r="N56">
-        <v>-82.94590386666667</v>
+        <v>-85.59181566666666</v>
       </c>
       <c r="O56">
-        <v>-18.24809885066667</v>
+        <v>-18.83019944666666</v>
       </c>
       <c r="P56">
-        <v>-64.697805016</v>
+        <v>-66.76161621999999</v>
       </c>
       <c r="Q56">
-        <v>9.202194984000002</v>
+        <v>7.138383780000012</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1267794288213543</v>
+        <v>0.1285789716840511</v>
       </c>
       <c r="T56">
-        <v>1.870194661001255</v>
+        <v>1.911754542356839</v>
       </c>
       <c r="U56">
         <v>0.2358</v>
       </c>
       <c r="V56">
-        <v>0.09228306079823706</v>
+        <v>0.09060518696554185</v>
       </c>
       <c r="W56">
-        <v>0.2140396542637757</v>
+        <v>0.2144352969135252</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -6036,7 +6036,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.4194684581738048</v>
+        <v>0.4118417589342811</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6044,22 +6044,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1757999505602619</v>
+        <v>0.1776999505602619</v>
       </c>
       <c r="C57">
-        <v>-243.8210371367833</v>
+        <v>-259.0062981864705</v>
       </c>
       <c r="D57">
-        <v>285.0339628632167</v>
+        <v>281.0697018135295</v>
       </c>
       <c r="E57">
-        <v>-56.04500000000007</v>
+        <v>-44.82400000000007</v>
       </c>
       <c r="F57">
-        <v>617.155</v>
+        <v>628.376</v>
       </c>
       <c r="G57">
         <v>88.3</v>
@@ -6080,37 +6080,37 @@
         <v>59.93333333333334</v>
       </c>
       <c r="M57">
-        <v>145.525149</v>
+        <v>148.1710608</v>
       </c>
       <c r="N57">
-        <v>-85.59181566666666</v>
+        <v>-88.23772746666666</v>
       </c>
       <c r="O57">
-        <v>-18.83019944666666</v>
+        <v>-19.41230004266666</v>
       </c>
       <c r="P57">
-        <v>-66.76161621999999</v>
+        <v>-68.825427424</v>
       </c>
       <c r="Q57">
-        <v>7.138383780000012</v>
+        <v>5.074572576000008</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1285789716840511</v>
+        <v>0.1304603119495977</v>
       </c>
       <c r="T57">
-        <v>1.911754542356839</v>
+        <v>1.955203509228585</v>
       </c>
       <c r="U57">
         <v>0.2358</v>
       </c>
       <c r="V57">
-        <v>0.09060518696554185</v>
+        <v>0.08898723719830003</v>
       </c>
       <c r="W57">
-        <v>0.2144352969135252</v>
+        <v>0.2148168094686408</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -6118,7 +6118,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.4118417589342811</v>
+        <v>0.4044874418104547</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6126,22 +6126,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1776999505602619</v>
+        <v>0.1795999505602619</v>
       </c>
       <c r="C58">
-        <v>-259.0062981864705</v>
+        <v>-274.0828017119259</v>
       </c>
       <c r="D58">
-        <v>281.0697018135295</v>
+        <v>277.214198288074</v>
       </c>
       <c r="E58">
-        <v>-44.82400000000007</v>
+        <v>-33.60300000000007</v>
       </c>
       <c r="F58">
-        <v>628.376</v>
+        <v>639.597</v>
       </c>
       <c r="G58">
         <v>88.3</v>
@@ -6162,37 +6162,37 @@
         <v>59.93333333333334</v>
       </c>
       <c r="M58">
-        <v>148.1710608</v>
+        <v>150.8169726</v>
       </c>
       <c r="N58">
-        <v>-88.23772746666666</v>
+        <v>-90.88363926666668</v>
       </c>
       <c r="O58">
-        <v>-19.41230004266666</v>
+        <v>-19.99440063866667</v>
       </c>
       <c r="P58">
-        <v>-68.825427424</v>
+        <v>-70.88923862800002</v>
       </c>
       <c r="Q58">
-        <v>5.074572576000008</v>
+        <v>3.01076137199999</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1304603119495977</v>
+        <v>0.1324291564135419</v>
       </c>
       <c r="T58">
-        <v>1.955203509228585</v>
+        <v>2.000673358280412</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>0.08898723719830003</v>
+        <v>0.08742605759832985</v>
       </c>
       <c r="W58">
-        <v>0.2148168094686408</v>
+        <v>0.2151849356183138</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6200,7 +6200,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.4044874418104547</v>
+        <v>0.3973911709014992</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6208,22 +6208,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1795999505602619</v>
+        <v>0.1814999505602619</v>
       </c>
       <c r="C59">
-        <v>-274.0828017119259</v>
+        <v>-289.0549627141068</v>
       </c>
       <c r="D59">
-        <v>277.214198288074</v>
+        <v>273.4630372858932</v>
       </c>
       <c r="E59">
-        <v>-33.60300000000007</v>
+        <v>-22.38200000000006</v>
       </c>
       <c r="F59">
-        <v>639.597</v>
+        <v>650.818</v>
       </c>
       <c r="G59">
         <v>88.3</v>
@@ -6244,37 +6244,37 @@
         <v>59.93333333333334</v>
       </c>
       <c r="M59">
-        <v>150.8169726</v>
+        <v>153.4628844</v>
       </c>
       <c r="N59">
-        <v>-90.88363926666668</v>
+        <v>-93.52955106666667</v>
       </c>
       <c r="O59">
-        <v>-19.99440063866667</v>
+        <v>-20.57650123466667</v>
       </c>
       <c r="P59">
-        <v>-70.88923862800002</v>
+        <v>-72.953049832</v>
       </c>
       <c r="Q59">
-        <v>3.01076137199999</v>
+        <v>0.9469501680000008</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1324291564135419</v>
+        <v>0.134491755375769</v>
       </c>
       <c r="T59">
-        <v>2.000673358280412</v>
+        <v>2.04830843823947</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>0.08742605759832985</v>
+        <v>0.08591871177766899</v>
       </c>
       <c r="W59">
-        <v>0.2151849356183138</v>
+        <v>0.2155403677628257</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6282,7 +6282,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.3973911709014992</v>
+        <v>0.3905395989894045</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6290,22 +6290,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1814999505602619</v>
+        <v>0.1833999505602618</v>
       </c>
       <c r="C60">
-        <v>-289.0549627141066</v>
+        <v>-303.926960415731</v>
       </c>
       <c r="D60">
-        <v>273.4630372858932</v>
+        <v>269.8120395842689</v>
       </c>
       <c r="E60">
-        <v>-22.38200000000018</v>
+        <v>-11.16100000000017</v>
       </c>
       <c r="F60">
-        <v>650.8179999999999</v>
+        <v>662.0389999999999</v>
       </c>
       <c r="G60">
         <v>88.3</v>
@@ -6326,37 +6326,37 @@
         <v>59.93333333333334</v>
       </c>
       <c r="M60">
-        <v>153.4628844</v>
+        <v>156.1087962</v>
       </c>
       <c r="N60">
-        <v>-93.52955106666664</v>
+        <v>-96.17546286666663</v>
       </c>
       <c r="O60">
-        <v>-20.57650123466666</v>
+        <v>-21.15860183066666</v>
       </c>
       <c r="P60">
-        <v>-72.95304983199998</v>
+        <v>-75.01686103599998</v>
       </c>
       <c r="Q60">
-        <v>0.9469501680000292</v>
+        <v>-1.116861035999975</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.134491755375769</v>
+        <v>0.1366549689215195</v>
       </c>
       <c r="T60">
-        <v>2.048308438239469</v>
+        <v>2.098267180635554</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>0.08591871177766901</v>
+        <v>0.08446246242550512</v>
       </c>
       <c r="W60">
-        <v>0.2155403677628257</v>
+        <v>0.2158837513600659</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6364,7 +6364,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.3905395989894045</v>
+        <v>0.383920283752296</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6372,22 +6372,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1833999505602618</v>
+        <v>0.1852999505602619</v>
       </c>
       <c r="C61">
-        <v>-303.926960415731</v>
+        <v>-318.7027537932556</v>
       </c>
       <c r="D61">
-        <v>269.8120395842689</v>
+        <v>266.2572462067443</v>
       </c>
       <c r="E61">
-        <v>-11.16100000000017</v>
+        <v>0.05999999999983174</v>
       </c>
       <c r="F61">
-        <v>662.0389999999999</v>
+        <v>673.2599999999999</v>
       </c>
       <c r="G61">
         <v>88.3</v>
@@ -6408,37 +6408,37 @@
         <v>59.93333333333334</v>
       </c>
       <c r="M61">
-        <v>156.1087962</v>
+        <v>158.754708</v>
       </c>
       <c r="N61">
-        <v>-96.17546286666663</v>
+        <v>-98.82137466666663</v>
       </c>
       <c r="O61">
-        <v>-21.15860183066666</v>
+        <v>-21.74070242666666</v>
       </c>
       <c r="P61">
-        <v>-75.01686103599998</v>
+        <v>-77.08067223999997</v>
       </c>
       <c r="Q61">
-        <v>-1.116861035999975</v>
+        <v>-3.180672239999964</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1366549689215195</v>
+        <v>0.1389263431445575</v>
       </c>
       <c r="T61">
-        <v>2.098267180635554</v>
+        <v>2.150723860151443</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.08446246242550512</v>
+        <v>0.08305475471841336</v>
       </c>
       <c r="W61">
-        <v>0.2158837513600659</v>
+        <v>0.2162156888373981</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6446,7 +6446,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.383920283752296</v>
+        <v>0.3775216123564245</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6454,22 +6454,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1852999505602619</v>
+        <v>0.1871999505602619</v>
       </c>
       <c r="C62">
-        <v>-318.7027537932556</v>
+        <v>-333.3860958970102</v>
       </c>
       <c r="D62">
-        <v>266.2572462067443</v>
+        <v>262.7949041029897</v>
       </c>
       <c r="E62">
-        <v>0.05999999999983174</v>
+        <v>11.28099999999984</v>
       </c>
       <c r="F62">
-        <v>673.2599999999999</v>
+        <v>684.4809999999999</v>
       </c>
       <c r="G62">
         <v>88.3</v>
@@ -6490,37 +6490,37 @@
         <v>59.93333333333334</v>
       </c>
       <c r="M62">
-        <v>158.754708</v>
+        <v>161.4006198</v>
       </c>
       <c r="N62">
-        <v>-98.82137466666663</v>
+        <v>-101.4672864666666</v>
       </c>
       <c r="O62">
-        <v>-21.74070242666666</v>
+        <v>-22.32280302266666</v>
       </c>
       <c r="P62">
-        <v>-77.08067223999997</v>
+        <v>-79.14448344399999</v>
       </c>
       <c r="Q62">
-        <v>-3.180672239999964</v>
+        <v>-5.244483443999982</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1389263431445575</v>
+        <v>0.141314198096982</v>
       </c>
       <c r="T62">
-        <v>2.150723860151443</v>
+        <v>2.205870625796352</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.08305475471841336</v>
+        <v>0.0816932013623738</v>
       </c>
       <c r="W62">
-        <v>0.2162156888373981</v>
+        <v>0.2165367431187523</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6528,7 +6528,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.3775216123564245</v>
+        <v>0.3713327334653355</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6536,22 +6536,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1871999505602619</v>
+        <v>0.1890999505602619</v>
       </c>
       <c r="C63">
-        <v>-333.3860958970102</v>
+        <v>-347.9805470683819</v>
       </c>
       <c r="D63">
-        <v>262.7949041029897</v>
+        <v>259.421452931618</v>
       </c>
       <c r="E63">
-        <v>11.28099999999984</v>
+        <v>22.50199999999984</v>
       </c>
       <c r="F63">
-        <v>684.4809999999999</v>
+        <v>695.7019999999999</v>
       </c>
       <c r="G63">
         <v>88.3</v>
@@ -6572,37 +6572,37 @@
         <v>59.93333333333334</v>
       </c>
       <c r="M63">
-        <v>161.4006198</v>
+        <v>164.0465316</v>
       </c>
       <c r="N63">
-        <v>-101.4672864666666</v>
+        <v>-104.1131982666666</v>
       </c>
       <c r="O63">
-        <v>-22.32280302266666</v>
+        <v>-22.90490361866666</v>
       </c>
       <c r="P63">
-        <v>-79.14448344399999</v>
+        <v>-81.20829464799998</v>
       </c>
       <c r="Q63">
-        <v>-5.244483443999982</v>
+        <v>-7.308294647999972</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.141314198096982</v>
+        <v>0.14382772962585</v>
       </c>
       <c r="T63">
-        <v>2.205870625796352</v>
+        <v>2.263919852790993</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.0816932013623738</v>
+        <v>0.08037556908233551</v>
       </c>
       <c r="W63">
-        <v>0.2165367431187523</v>
+        <v>0.2168474408103853</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6610,7 +6610,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.3713327334653355</v>
+        <v>0.3653434958287978</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6618,22 +6618,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1890999505602619</v>
+        <v>0.1909999505602619</v>
       </c>
       <c r="C64">
-        <v>-347.9805470683819</v>
+        <v>-362.4894871519017</v>
       </c>
       <c r="D64">
-        <v>259.421452931618</v>
+        <v>256.1335128480983</v>
       </c>
       <c r="E64">
-        <v>22.50199999999984</v>
+        <v>33.72299999999996</v>
       </c>
       <c r="F64">
-        <v>695.7019999999999</v>
+        <v>706.923</v>
       </c>
       <c r="G64">
         <v>88.3</v>
@@ -6654,37 +6654,37 @@
         <v>59.93333333333334</v>
       </c>
       <c r="M64">
-        <v>164.0465316</v>
+        <v>166.6924434</v>
       </c>
       <c r="N64">
-        <v>-104.1131982666666</v>
+        <v>-106.7591100666667</v>
       </c>
       <c r="O64">
-        <v>-22.90490361866666</v>
+        <v>-23.48700421466667</v>
       </c>
       <c r="P64">
-        <v>-81.20829464799998</v>
+        <v>-83.272105852</v>
       </c>
       <c r="Q64">
-        <v>-7.308294647999972</v>
+        <v>-9.37210585199999</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.14382772962585</v>
+        <v>0.1464771277238459</v>
       </c>
       <c r="T64">
-        <v>2.263919852790993</v>
+        <v>2.325106875839398</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.08037556908233551</v>
+        <v>0.07909976639848891</v>
       </c>
       <c r="W64">
-        <v>0.2168474408103853</v>
+        <v>0.2171482750832363</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6692,7 +6692,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.3653434958287978</v>
+        <v>0.3595443927204042</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6700,22 +6700,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1909999505602619</v>
+        <v>0.1928999505602619</v>
       </c>
       <c r="C65">
-        <v>-362.4894871519017</v>
+        <v>-376.916126790289</v>
       </c>
       <c r="D65">
-        <v>256.1335128480983</v>
+        <v>252.927873209711</v>
       </c>
       <c r="E65">
-        <v>33.72299999999996</v>
+        <v>44.94399999999996</v>
       </c>
       <c r="F65">
-        <v>706.923</v>
+        <v>718.144</v>
       </c>
       <c r="G65">
         <v>88.3</v>
@@ -6736,37 +6736,37 @@
         <v>59.93333333333334</v>
       </c>
       <c r="M65">
-        <v>166.6924434</v>
+        <v>169.3383552</v>
       </c>
       <c r="N65">
-        <v>-106.7591100666667</v>
+        <v>-109.4050218666667</v>
       </c>
       <c r="O65">
-        <v>-23.48700421466667</v>
+        <v>-24.06910481066667</v>
       </c>
       <c r="P65">
-        <v>-83.272105852</v>
+        <v>-85.335917056</v>
       </c>
       <c r="Q65">
-        <v>-9.37210585199999</v>
+        <v>-11.43591705599999</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1464771277238459</v>
+        <v>0.1492737146050639</v>
       </c>
       <c r="T65">
-        <v>2.325106875839398</v>
+        <v>2.389693177946048</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.07909976639848891</v>
+        <v>0.07786383254851252</v>
       </c>
       <c r="W65">
-        <v>0.2171482750832363</v>
+        <v>0.2174397082850608</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6774,7 +6774,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.3595443927204042</v>
+        <v>0.3539265115841478</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6782,22 +6782,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1928999505602619</v>
+        <v>0.1947999505602619</v>
       </c>
       <c r="C66">
-        <v>-376.916126790289</v>
+        <v>-391.2635178818012</v>
       </c>
       <c r="D66">
-        <v>252.927873209711</v>
+        <v>249.8014821181988</v>
       </c>
       <c r="E66">
-        <v>44.94399999999996</v>
+        <v>56.16499999999996</v>
       </c>
       <c r="F66">
-        <v>718.144</v>
+        <v>729.365</v>
       </c>
       <c r="G66">
         <v>88.3</v>
@@ -6818,37 +6818,37 @@
         <v>59.93333333333334</v>
       </c>
       <c r="M66">
-        <v>169.3383552</v>
+        <v>171.984267</v>
       </c>
       <c r="N66">
-        <v>-109.4050218666667</v>
+        <v>-112.0509336666667</v>
       </c>
       <c r="O66">
-        <v>-24.06910481066667</v>
+        <v>-24.65120540666667</v>
       </c>
       <c r="P66">
-        <v>-85.335917056</v>
+        <v>-87.39972826000002</v>
       </c>
       <c r="Q66">
-        <v>-11.43591705599999</v>
+        <v>-13.49972826000001</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1492737146050639</v>
+        <v>0.1522301064509228</v>
       </c>
       <c r="T66">
-        <v>2.389693177946048</v>
+        <v>2.457970125887364</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.07786383254851252</v>
+        <v>0.07666592743238156</v>
       </c>
       <c r="W66">
-        <v>0.2174397082850608</v>
+        <v>0.2177221743114444</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6856,7 +6856,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.3539265115841478</v>
+        <v>0.348481488329007</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6864,22 +6864,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1947999505602619</v>
+        <v>0.1966999505602619</v>
       </c>
       <c r="C67">
-        <v>-391.2635178818012</v>
+        <v>-405.5345632714851</v>
       </c>
       <c r="D67">
-        <v>249.8014821181988</v>
+        <v>246.751436728515</v>
       </c>
       <c r="E67">
-        <v>56.16499999999996</v>
+        <v>67.38599999999997</v>
       </c>
       <c r="F67">
-        <v>729.365</v>
+        <v>740.586</v>
       </c>
       <c r="G67">
         <v>88.3</v>
@@ -6900,37 +6900,37 @@
         <v>59.93333333333334</v>
       </c>
       <c r="M67">
-        <v>171.984267</v>
+        <v>174.6301788</v>
       </c>
       <c r="N67">
-        <v>-112.0509336666667</v>
+        <v>-114.6968454666667</v>
       </c>
       <c r="O67">
-        <v>-24.65120540666667</v>
+        <v>-25.23330600266667</v>
       </c>
       <c r="P67">
-        <v>-87.39972826000002</v>
+        <v>-89.46353946400001</v>
       </c>
       <c r="Q67">
-        <v>-13.49972826000001</v>
+        <v>-15.563539464</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1522301064509228</v>
+        <v>0.1553604036994794</v>
       </c>
       <c r="T67">
-        <v>2.457970125887364</v>
+        <v>2.530263364884051</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.07666592743238156</v>
+        <v>0.07550432247128487</v>
       </c>
       <c r="W67">
-        <v>0.2177221743114444</v>
+        <v>0.217996080761271</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6938,7 +6938,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.348481488329007</v>
+        <v>0.3432014657785676</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6946,22 +6946,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1966999505602619</v>
+        <v>0.1985999505602619</v>
       </c>
       <c r="C68">
-        <v>-405.5345632714851</v>
+        <v>-419.7320257410196</v>
       </c>
       <c r="D68">
-        <v>246.751436728515</v>
+        <v>243.7749742589804</v>
       </c>
       <c r="E68">
-        <v>67.38599999999997</v>
+        <v>78.60699999999997</v>
       </c>
       <c r="F68">
-        <v>740.586</v>
+        <v>751.807</v>
       </c>
       <c r="G68">
         <v>88.3</v>
@@ -6982,37 +6982,37 @@
         <v>59.93333333333334</v>
       </c>
       <c r="M68">
-        <v>174.6301788</v>
+        <v>177.2760906</v>
       </c>
       <c r="N68">
-        <v>-114.6968454666667</v>
+        <v>-117.3427572666667</v>
       </c>
       <c r="O68">
-        <v>-25.23330600266667</v>
+        <v>-25.81540659866667</v>
       </c>
       <c r="P68">
-        <v>-89.46353946400001</v>
+        <v>-91.527350668</v>
       </c>
       <c r="Q68">
-        <v>-15.563539464</v>
+        <v>-17.62735066799999</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1553604036994794</v>
+        <v>0.158680415932797</v>
       </c>
       <c r="T68">
-        <v>2.530263364884051</v>
+        <v>2.60693801230478</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.07550432247128487</v>
+        <v>0.0743773922851463</v>
       </c>
       <c r="W68">
-        <v>0.217996080761271</v>
+        <v>0.2182618108991625</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -7020,7 +7020,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.3432014657785676</v>
+        <v>0.338079055841574</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7028,22 +7028,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1985999505602619</v>
+        <v>0.2004999505602619</v>
       </c>
       <c r="C69">
-        <v>-419.7320257410196</v>
+        <v>-433.8585363556672</v>
       </c>
       <c r="D69">
-        <v>243.7749742589804</v>
+        <v>240.8694636443328</v>
       </c>
       <c r="E69">
-        <v>78.60699999999997</v>
+        <v>89.82799999999997</v>
       </c>
       <c r="F69">
-        <v>751.807</v>
+        <v>763.028</v>
       </c>
       <c r="G69">
         <v>88.3</v>
@@ -7064,37 +7064,37 @@
         <v>59.93333333333334</v>
       </c>
       <c r="M69">
-        <v>177.2760906</v>
+        <v>179.9220024</v>
       </c>
       <c r="N69">
-        <v>-117.3427572666667</v>
+        <v>-119.9886690666667</v>
       </c>
       <c r="O69">
-        <v>-25.81540659866667</v>
+        <v>-26.39750719466667</v>
       </c>
       <c r="P69">
-        <v>-91.527350668</v>
+        <v>-93.59116187200001</v>
       </c>
       <c r="Q69">
-        <v>-17.62735066799999</v>
+        <v>-19.69116187200001</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.158680415932797</v>
+        <v>0.1622079289306969</v>
       </c>
       <c r="T69">
-        <v>2.60693801230478</v>
+        <v>2.688404825189305</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.0743773922851463</v>
+        <v>0.07328360710448237</v>
       </c>
       <c r="W69">
-        <v>0.2182618108991625</v>
+        <v>0.2185197254447631</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -7102,7 +7102,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.338079055841574</v>
+        <v>0.3331073050203743</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7110,22 +7110,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2004999505602619</v>
+        <v>0.2023999505602619</v>
       </c>
       <c r="C70">
-        <v>-433.8585363556672</v>
+        <v>-447.9166022213421</v>
       </c>
       <c r="D70">
-        <v>240.8694636443328</v>
+        <v>238.0323977786579</v>
       </c>
       <c r="E70">
-        <v>89.82799999999997</v>
+        <v>101.049</v>
       </c>
       <c r="F70">
-        <v>763.028</v>
+        <v>774.249</v>
       </c>
       <c r="G70">
         <v>88.3</v>
@@ -7146,37 +7146,37 @@
         <v>59.93333333333334</v>
       </c>
       <c r="M70">
-        <v>179.9220024</v>
+        <v>182.5679142</v>
       </c>
       <c r="N70">
-        <v>-119.9886690666667</v>
+        <v>-122.6345808666667</v>
       </c>
       <c r="O70">
-        <v>-26.39750719466667</v>
+        <v>-26.97960779066667</v>
       </c>
       <c r="P70">
-        <v>-93.59116187200001</v>
+        <v>-95.654973076</v>
       </c>
       <c r="Q70">
-        <v>-19.69116187200001</v>
+        <v>-21.754973076</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1622079289306969</v>
+        <v>0.1659630234123322</v>
       </c>
       <c r="T70">
-        <v>2.688404825189305</v>
+        <v>2.775127561485733</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.07328360710448237</v>
+        <v>0.07222152584209855</v>
       </c>
       <c r="W70">
-        <v>0.2185197254447631</v>
+        <v>0.2187701642064332</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7184,7 +7184,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.3331073050203743</v>
+        <v>0.3282796629186299</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7192,22 +7192,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2023999505602619</v>
+        <v>0.2042999505602619</v>
       </c>
       <c r="C71">
-        <v>-447.9166022213421</v>
+        <v>-461.9086136998624</v>
       </c>
       <c r="D71">
-        <v>238.0323977786579</v>
+        <v>235.2613863001376</v>
       </c>
       <c r="E71">
-        <v>101.049</v>
+        <v>112.27</v>
       </c>
       <c r="F71">
-        <v>774.249</v>
+        <v>785.47</v>
       </c>
       <c r="G71">
         <v>88.3</v>
@@ -7228,37 +7228,37 @@
         <v>59.93333333333334</v>
       </c>
       <c r="M71">
-        <v>182.5679142</v>
+        <v>185.213826</v>
       </c>
       <c r="N71">
-        <v>-122.6345808666667</v>
+        <v>-125.2804926666667</v>
       </c>
       <c r="O71">
-        <v>-26.97960779066667</v>
+        <v>-27.56170838666667</v>
       </c>
       <c r="P71">
-        <v>-95.654973076</v>
+        <v>-97.71878428000001</v>
       </c>
       <c r="Q71">
-        <v>-21.754973076</v>
+        <v>-23.81878428</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1659630234123322</v>
+        <v>0.1699684575260767</v>
       </c>
       <c r="T71">
-        <v>2.775127561485733</v>
+        <v>2.867631813535258</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.07222152584209855</v>
+        <v>0.07118978975864002</v>
       </c>
       <c r="W71">
-        <v>0.2187701642064332</v>
+        <v>0.2190134475749127</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7266,7 +7266,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.3282796629186299</v>
+        <v>0.3235899534483637</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7274,22 +7274,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2042999505602619</v>
+        <v>0.2061999505602619</v>
       </c>
       <c r="C72">
-        <v>-461.9086136998624</v>
+        <v>-475.8368511260321</v>
       </c>
       <c r="D72">
-        <v>235.2613863001376</v>
+        <v>232.554148873968</v>
       </c>
       <c r="E72">
-        <v>112.27</v>
+        <v>123.491</v>
       </c>
       <c r="F72">
-        <v>785.47</v>
+        <v>796.691</v>
       </c>
       <c r="G72">
         <v>88.3</v>
@@ -7310,37 +7310,37 @@
         <v>59.93333333333334</v>
       </c>
       <c r="M72">
-        <v>185.213826</v>
+        <v>187.8597378</v>
       </c>
       <c r="N72">
-        <v>-125.2804926666667</v>
+        <v>-127.9264044666667</v>
       </c>
       <c r="O72">
-        <v>-27.56170838666667</v>
+        <v>-28.14380898266667</v>
       </c>
       <c r="P72">
-        <v>-97.71878428000001</v>
+        <v>-99.782595484</v>
       </c>
       <c r="Q72">
-        <v>-23.81878428</v>
+        <v>-25.88259548399999</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1699684575260767</v>
+        <v>0.1742501284752518</v>
       </c>
       <c r="T72">
-        <v>2.867631813535258</v>
+        <v>2.966515669174405</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.07118978975864002</v>
+        <v>0.0701871166634479</v>
       </c>
       <c r="W72">
-        <v>0.2190134475749127</v>
+        <v>0.219249877890759</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7348,7 +7348,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.3235899534483637</v>
+        <v>0.3190323484702178</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7356,22 +7356,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2061999505602619</v>
+        <v>0.2080999505602619</v>
       </c>
       <c r="C73">
-        <v>-475.8368511260321</v>
+        <v>-489.703491066223</v>
       </c>
       <c r="D73">
-        <v>232.5541488739678</v>
+        <v>229.9085089337769</v>
       </c>
       <c r="E73">
-        <v>123.4909999999999</v>
+        <v>134.7119999999999</v>
       </c>
       <c r="F73">
-        <v>796.6909999999999</v>
+        <v>807.9119999999999</v>
       </c>
       <c r="G73">
         <v>88.3</v>
@@ -7392,37 +7392,37 @@
         <v>59.93333333333334</v>
       </c>
       <c r="M73">
-        <v>187.8597378</v>
+        <v>190.5056496</v>
       </c>
       <c r="N73">
-        <v>-127.9264044666666</v>
+        <v>-130.5723162666667</v>
       </c>
       <c r="O73">
-        <v>-28.14380898266666</v>
+        <v>-28.72590957866667</v>
       </c>
       <c r="P73">
-        <v>-99.78259548399998</v>
+        <v>-101.846406688</v>
       </c>
       <c r="Q73">
-        <v>-25.88259548399998</v>
+        <v>-27.946406688</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1742501284752517</v>
+        <v>0.1788376330636536</v>
       </c>
       <c r="T73">
-        <v>2.966515669174404</v>
+        <v>3.072462657359204</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.07018711666344792</v>
+        <v>0.06921229559867779</v>
       </c>
       <c r="W73">
-        <v>0.219249877890759</v>
+        <v>0.2194797406978318</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7430,7 +7430,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.3190323484702178</v>
+        <v>0.3146013436303536</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7438,22 +7438,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2080999505602619</v>
+        <v>0.2099999505602619</v>
       </c>
       <c r="C74">
-        <v>-489.703491066223</v>
+        <v>-503.5106121545612</v>
       </c>
       <c r="D74">
-        <v>229.9085089337769</v>
+        <v>227.3223878454387</v>
       </c>
       <c r="E74">
-        <v>134.7119999999999</v>
+        <v>145.9329999999999</v>
       </c>
       <c r="F74">
-        <v>807.9119999999999</v>
+        <v>819.1329999999999</v>
       </c>
       <c r="G74">
         <v>88.3</v>
@@ -7474,37 +7474,37 @@
         <v>59.93333333333334</v>
       </c>
       <c r="M74">
-        <v>190.5056496</v>
+        <v>193.1515614</v>
       </c>
       <c r="N74">
-        <v>-130.5723162666667</v>
+        <v>-133.2182280666667</v>
       </c>
       <c r="O74">
-        <v>-28.72590957866667</v>
+        <v>-29.30801017466666</v>
       </c>
       <c r="P74">
-        <v>-101.846406688</v>
+        <v>-103.910217892</v>
       </c>
       <c r="Q74">
-        <v>-27.946406688</v>
+        <v>-30.01021789199999</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1788376330636536</v>
+        <v>0.1837649528067518</v>
       </c>
       <c r="T74">
-        <v>3.072462657359204</v>
+        <v>3.18625757059473</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.06921229559867779</v>
+        <v>0.06826418196033975</v>
       </c>
       <c r="W74">
-        <v>0.2194797406978318</v>
+        <v>0.2197033058937519</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7512,7 +7512,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.3146013436303536</v>
+        <v>0.3102917361833625</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7520,22 +7520,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2099999505602619</v>
+        <v>0.2118999505602619</v>
       </c>
       <c r="C75">
-        <v>-503.5106121545612</v>
+        <v>-517.260200539603</v>
       </c>
       <c r="D75">
-        <v>227.3223878454387</v>
+        <v>224.7937994603969</v>
       </c>
       <c r="E75">
-        <v>145.9329999999999</v>
+        <v>157.1539999999999</v>
       </c>
       <c r="F75">
-        <v>819.1329999999999</v>
+        <v>830.3539999999999</v>
       </c>
       <c r="G75">
         <v>88.3</v>
@@ -7556,37 +7556,37 @@
         <v>59.93333333333334</v>
       </c>
       <c r="M75">
-        <v>193.1515614</v>
+        <v>195.7974732</v>
       </c>
       <c r="N75">
-        <v>-133.2182280666667</v>
+        <v>-135.8641398666666</v>
       </c>
       <c r="O75">
-        <v>-29.30801017466666</v>
+        <v>-29.89011077066666</v>
       </c>
       <c r="P75">
-        <v>-103.910217892</v>
+        <v>-105.974029096</v>
       </c>
       <c r="Q75">
-        <v>-30.01021789199999</v>
+        <v>-32.07402909599998</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1837649528067518</v>
+        <v>0.189071297145473</v>
       </c>
       <c r="T75">
-        <v>3.18625757059473</v>
+        <v>3.308805938694527</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.06826418196033975</v>
+        <v>0.06734169301492976</v>
       </c>
       <c r="W75">
-        <v>0.2197033058937519</v>
+        <v>0.2199208287870796</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7594,7 +7594,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.3102917361833625</v>
+        <v>0.3060986046133171</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7602,22 +7602,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2118999505602619</v>
+        <v>0.2137999505602619</v>
       </c>
       <c r="C76">
-        <v>-517.260200539603</v>
+        <v>-530.9541549714997</v>
       </c>
       <c r="D76">
-        <v>224.7937994603969</v>
+        <v>222.3208450285001</v>
       </c>
       <c r="E76">
-        <v>157.1539999999999</v>
+        <v>168.3749999999999</v>
       </c>
       <c r="F76">
-        <v>830.3539999999999</v>
+        <v>841.5749999999999</v>
       </c>
       <c r="G76">
         <v>88.3</v>
@@ -7638,37 +7638,37 @@
         <v>59.93333333333334</v>
       </c>
       <c r="M76">
-        <v>195.7974732</v>
+        <v>198.443385</v>
       </c>
       <c r="N76">
-        <v>-135.8641398666666</v>
+        <v>-138.5100516666666</v>
       </c>
       <c r="O76">
-        <v>-29.89011077066666</v>
+        <v>-30.47221136666666</v>
       </c>
       <c r="P76">
-        <v>-105.974029096</v>
+        <v>-108.0378403</v>
       </c>
       <c r="Q76">
-        <v>-32.07402909599998</v>
+        <v>-34.13784029999998</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.189071297145473</v>
+        <v>0.194802149031292</v>
       </c>
       <c r="T76">
-        <v>3.308805938694527</v>
+        <v>3.441158176242309</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.06734169301492976</v>
+        <v>0.06644380377473069</v>
       </c>
       <c r="W76">
-        <v>0.2199208287870796</v>
+        <v>0.2201325510699185</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7676,7 +7676,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.3060986046133171</v>
+        <v>0.3020172898851395</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7684,22 +7684,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2137999505602619</v>
+        <v>0.2156999505602619</v>
       </c>
       <c r="C77">
-        <v>-530.9541549714997</v>
+        <v>-544.5942915570331</v>
       </c>
       <c r="D77">
-        <v>222.3208450285001</v>
+        <v>219.9017084429669</v>
       </c>
       <c r="E77">
-        <v>168.3749999999999</v>
+        <v>179.5959999999999</v>
       </c>
       <c r="F77">
-        <v>841.5749999999999</v>
+        <v>852.7959999999999</v>
       </c>
       <c r="G77">
         <v>88.3</v>
@@ -7720,37 +7720,37 @@
         <v>59.93333333333334</v>
       </c>
       <c r="M77">
-        <v>198.443385</v>
+        <v>201.0892968</v>
       </c>
       <c r="N77">
-        <v>-138.5100516666666</v>
+        <v>-141.1559634666667</v>
       </c>
       <c r="O77">
-        <v>-30.47221136666666</v>
+        <v>-31.05431196266667</v>
       </c>
       <c r="P77">
-        <v>-108.0378403</v>
+        <v>-110.101651504</v>
       </c>
       <c r="Q77">
-        <v>-34.13784029999998</v>
+        <v>-36.20165150399998</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.194802149031292</v>
+        <v>0.2010105719075958</v>
       </c>
       <c r="T77">
-        <v>3.441158176242309</v>
+        <v>3.584539766919072</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.06644380377473069</v>
+        <v>0.06556954319874739</v>
       </c>
       <c r="W77">
-        <v>0.2201325510699185</v>
+        <v>0.2203387017137354</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7758,7 +7758,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.3020172898851395</v>
+        <v>0.2980433781761245</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7766,22 +7766,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2156999505602619</v>
+        <v>0.2175999505602619</v>
       </c>
       <c r="C78">
-        <v>-544.5942915570331</v>
+        <v>-558.1823482075462</v>
       </c>
       <c r="D78">
-        <v>219.9017084429669</v>
+        <v>217.5346517924538</v>
       </c>
       <c r="E78">
-        <v>179.5959999999999</v>
+        <v>190.8169999999999</v>
       </c>
       <c r="F78">
-        <v>852.7959999999999</v>
+        <v>864.0169999999999</v>
       </c>
       <c r="G78">
         <v>88.3</v>
@@ -7802,37 +7802,37 @@
         <v>59.93333333333334</v>
       </c>
       <c r="M78">
-        <v>201.0892968</v>
+        <v>203.7352086</v>
       </c>
       <c r="N78">
-        <v>-141.1559634666667</v>
+        <v>-143.8018752666667</v>
       </c>
       <c r="O78">
-        <v>-31.05431196266667</v>
+        <v>-31.63641255866666</v>
       </c>
       <c r="P78">
-        <v>-110.101651504</v>
+        <v>-112.165462708</v>
       </c>
       <c r="Q78">
-        <v>-36.20165150399998</v>
+        <v>-38.26546270799999</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2010105719075958</v>
+        <v>0.2077588576427087</v>
       </c>
       <c r="T78">
-        <v>3.584539766919072</v>
+        <v>3.74038932200251</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.06556954319874739</v>
+        <v>0.06471799068967274</v>
       </c>
       <c r="W78">
-        <v>0.2203387017137354</v>
+        <v>0.2205394977953752</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7840,7 +7840,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.2980433781761245</v>
+        <v>0.2941726849530579</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7848,22 +7848,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2175999505602619</v>
+        <v>0.2194999505602619</v>
       </c>
       <c r="C79">
-        <v>-558.1823482075462</v>
+        <v>-571.7199888026644</v>
       </c>
       <c r="D79">
-        <v>217.5346517924538</v>
+        <v>215.2180111973355</v>
       </c>
       <c r="E79">
-        <v>190.8169999999999</v>
+        <v>202.0379999999999</v>
       </c>
       <c r="F79">
-        <v>864.0169999999999</v>
+        <v>875.2379999999999</v>
       </c>
       <c r="G79">
         <v>88.3</v>
@@ -7884,37 +7884,37 @@
         <v>59.93333333333334</v>
       </c>
       <c r="M79">
-        <v>203.7352086</v>
+        <v>206.3811204</v>
       </c>
       <c r="N79">
-        <v>-143.8018752666667</v>
+        <v>-146.4477870666666</v>
       </c>
       <c r="O79">
-        <v>-31.63641255866666</v>
+        <v>-32.21851315466666</v>
       </c>
       <c r="P79">
-        <v>-112.165462708</v>
+        <v>-114.229273912</v>
       </c>
       <c r="Q79">
-        <v>-38.26546270799999</v>
+        <v>-40.32927391199999</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2077588576427087</v>
+        <v>0.2151206238991955</v>
       </c>
       <c r="T79">
-        <v>3.74038932200251</v>
+        <v>3.91040701845717</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.06471799068967274</v>
+        <v>0.06388827286031797</v>
       </c>
       <c r="W79">
-        <v>0.2205394977953752</v>
+        <v>0.220735145259537</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7922,7 +7922,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.2941726849530579</v>
+        <v>0.2904012402741726</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7930,22 +7930,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2194999505602619</v>
+        <v>0.2213999505602619</v>
       </c>
       <c r="C80">
-        <v>-571.7199888026644</v>
+        <v>-585.2088070907707</v>
       </c>
       <c r="D80">
-        <v>215.2180111973355</v>
+        <v>212.9501929092292</v>
       </c>
       <c r="E80">
-        <v>202.0379999999999</v>
+        <v>213.2589999999999</v>
       </c>
       <c r="F80">
-        <v>875.2379999999999</v>
+        <v>886.4589999999999</v>
       </c>
       <c r="G80">
         <v>88.3</v>
@@ -7966,37 +7966,37 @@
         <v>59.93333333333334</v>
       </c>
       <c r="M80">
-        <v>206.3811204</v>
+        <v>209.0270322</v>
       </c>
       <c r="N80">
-        <v>-146.4477870666666</v>
+        <v>-149.0936988666667</v>
       </c>
       <c r="O80">
-        <v>-32.21851315466666</v>
+        <v>-32.80061375066667</v>
       </c>
       <c r="P80">
-        <v>-114.229273912</v>
+        <v>-116.293085116</v>
       </c>
       <c r="Q80">
-        <v>-40.32927391199999</v>
+        <v>-42.39308511599999</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2151206238991955</v>
+        <v>0.2231835107515381</v>
       </c>
       <c r="T80">
-        <v>3.91040701845717</v>
+        <v>4.09661687647894</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.06388827286031797</v>
+        <v>0.06307956054563039</v>
       </c>
       <c r="W80">
-        <v>0.220735145259537</v>
+        <v>0.2209258396233404</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -8004,7 +8004,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.2904012402741726</v>
+        <v>0.2867252752074109</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8012,22 +8012,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2213999505602619</v>
+        <v>0.2232999505602619</v>
       </c>
       <c r="C81">
-        <v>-585.2088070907707</v>
+        <v>-598.6503303454487</v>
       </c>
       <c r="D81">
-        <v>212.9501929092292</v>
+        <v>210.7296696545513</v>
       </c>
       <c r="E81">
-        <v>213.2589999999999</v>
+        <v>224.4799999999999</v>
       </c>
       <c r="F81">
-        <v>886.4589999999999</v>
+        <v>897.6799999999999</v>
       </c>
       <c r="G81">
         <v>88.3</v>
@@ -8048,37 +8048,37 @@
         <v>59.93333333333334</v>
       </c>
       <c r="M81">
-        <v>209.0270322</v>
+        <v>211.672944</v>
       </c>
       <c r="N81">
-        <v>-149.0936988666667</v>
+        <v>-151.7396106666667</v>
       </c>
       <c r="O81">
-        <v>-32.80061375066667</v>
+        <v>-33.38271434666667</v>
       </c>
       <c r="P81">
-        <v>-116.293085116</v>
+        <v>-118.35689632</v>
       </c>
       <c r="Q81">
-        <v>-42.39308511599999</v>
+        <v>-44.45689632</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2231835107515381</v>
+        <v>0.232052686289115</v>
       </c>
       <c r="T81">
-        <v>4.09661687647894</v>
+        <v>4.301447720302888</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.06307956054563039</v>
+        <v>0.06229106603881001</v>
       </c>
       <c r="W81">
-        <v>0.2209258396233404</v>
+        <v>0.2211117666280486</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -8086,7 +8086,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.2867252752074109</v>
+        <v>0.2831412092673182</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8094,22 +8094,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2232999505602619</v>
+        <v>0.2251999505602619</v>
       </c>
       <c r="C82">
-        <v>-598.6503303454487</v>
+        <v>-612.0460227955222</v>
       </c>
       <c r="D82">
-        <v>210.7296696545513</v>
+        <v>208.5549772044778</v>
       </c>
       <c r="E82">
-        <v>224.4799999999999</v>
+        <v>235.7009999999999</v>
       </c>
       <c r="F82">
-        <v>897.6799999999999</v>
+        <v>908.901</v>
       </c>
       <c r="G82">
         <v>88.3</v>
@@ -8130,37 +8130,37 @@
         <v>59.93333333333334</v>
       </c>
       <c r="M82">
-        <v>211.672944</v>
+        <v>214.3188558</v>
       </c>
       <c r="N82">
-        <v>-151.7396106666667</v>
+        <v>-154.3855224666667</v>
       </c>
       <c r="O82">
-        <v>-33.38271434666667</v>
+        <v>-33.96481494266666</v>
       </c>
       <c r="P82">
-        <v>-118.35689632</v>
+        <v>-120.420707524</v>
       </c>
       <c r="Q82">
-        <v>-44.45689632</v>
+        <v>-46.52070752399999</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.232052686289115</v>
+        <v>0.2418554592517</v>
       </c>
       <c r="T82">
-        <v>4.301447720302888</v>
+        <v>4.527839705581987</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.06229106603881001</v>
+        <v>0.06152204053215805</v>
       </c>
       <c r="W82">
-        <v>0.2211117666280486</v>
+        <v>0.2212931028425171</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8168,7 +8168,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.2831412092673182</v>
+        <v>0.2796456387825366</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8176,22 +8176,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2251999505602619</v>
+        <v>0.2270999505602619</v>
       </c>
       <c r="C83">
-        <v>-612.0460227955222</v>
+        <v>-625.3972888448804</v>
       </c>
       <c r="D83">
-        <v>208.5549772044778</v>
+        <v>206.4247111551195</v>
       </c>
       <c r="E83">
-        <v>235.7009999999999</v>
+        <v>246.9219999999999</v>
       </c>
       <c r="F83">
-        <v>908.901</v>
+        <v>920.122</v>
       </c>
       <c r="G83">
         <v>88.3</v>
@@ -8212,37 +8212,37 @@
         <v>59.93333333333334</v>
       </c>
       <c r="M83">
-        <v>214.3188558</v>
+        <v>216.9647676</v>
       </c>
       <c r="N83">
-        <v>-154.3855224666667</v>
+        <v>-157.0314342666667</v>
       </c>
       <c r="O83">
-        <v>-33.96481494266666</v>
+        <v>-34.54691553866666</v>
       </c>
       <c r="P83">
-        <v>-120.420707524</v>
+        <v>-122.484518728</v>
       </c>
       <c r="Q83">
-        <v>-46.52070752399999</v>
+        <v>-48.58451872799998</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2418554592517</v>
+        <v>0.2527474292101278</v>
       </c>
       <c r="T83">
-        <v>4.527839705581987</v>
+        <v>4.779386355892097</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.06152204053215805</v>
+        <v>0.0607717717451805</v>
       </c>
       <c r="W83">
-        <v>0.2212931028425171</v>
+        <v>0.2214700162224864</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8250,7 +8250,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.2796456387825366</v>
+        <v>0.2762353261144569</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8258,22 +8258,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2270999505602619</v>
+        <v>0.2289999505602619</v>
       </c>
       <c r="C84">
-        <v>-625.3972888448804</v>
+        <v>-638.7054760969679</v>
       </c>
       <c r="D84">
-        <v>206.4247111551195</v>
+        <v>204.337523903032</v>
       </c>
       <c r="E84">
-        <v>246.9219999999999</v>
+        <v>258.1429999999999</v>
       </c>
       <c r="F84">
-        <v>920.122</v>
+        <v>931.343</v>
       </c>
       <c r="G84">
         <v>88.3</v>
@@ -8294,37 +8294,37 @@
         <v>59.93333333333334</v>
       </c>
       <c r="M84">
-        <v>216.9647676</v>
+        <v>219.6106794</v>
       </c>
       <c r="N84">
-        <v>-157.0314342666667</v>
+        <v>-159.6773460666667</v>
       </c>
       <c r="O84">
-        <v>-34.54691553866666</v>
+        <v>-35.12901613466667</v>
       </c>
       <c r="P84">
-        <v>-122.484518728</v>
+        <v>-124.548329932</v>
       </c>
       <c r="Q84">
-        <v>-48.58451872799998</v>
+        <v>-50.648329932</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2527474292101278</v>
+        <v>0.2649208073989588</v>
       </c>
       <c r="T84">
-        <v>4.779386355892097</v>
+        <v>5.060526729768103</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.0607717717451805</v>
+        <v>0.06003958172415423</v>
       </c>
       <c r="W84">
-        <v>0.2214700162224864</v>
+        <v>0.2216426666294444</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8332,7 +8332,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.2762353261144569</v>
+        <v>0.2729071896552465</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8340,22 +8340,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2289999505602619</v>
+        <v>0.2308999505602619</v>
       </c>
       <c r="C85">
-        <v>-638.7054760969679</v>
+        <v>-651.9718781976226</v>
       </c>
       <c r="D85">
-        <v>204.337523903032</v>
+        <v>202.2921218023775</v>
       </c>
       <c r="E85">
-        <v>258.1429999999999</v>
+        <v>269.3639999999999</v>
       </c>
       <c r="F85">
-        <v>931.343</v>
+        <v>942.564</v>
       </c>
       <c r="G85">
         <v>88.3</v>
@@ -8376,37 +8376,37 @@
         <v>59.93333333333334</v>
       </c>
       <c r="M85">
-        <v>219.6106794</v>
+        <v>222.2565912</v>
       </c>
       <c r="N85">
-        <v>-159.6773460666667</v>
+        <v>-162.3232578666667</v>
       </c>
       <c r="O85">
-        <v>-35.12901613466667</v>
+        <v>-35.71111673066667</v>
       </c>
       <c r="P85">
-        <v>-124.548329932</v>
+        <v>-126.612141136</v>
       </c>
       <c r="Q85">
-        <v>-50.648329932</v>
+        <v>-52.71214113599999</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2649208073989588</v>
+        <v>0.2786158578613939</v>
       </c>
       <c r="T85">
-        <v>5.060526729768103</v>
+        <v>5.376809650378611</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.06003958172415423</v>
+        <v>0.05932482479886668</v>
       </c>
       <c r="W85">
-        <v>0.2216426666294444</v>
+        <v>0.2218112063124272</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8414,7 +8414,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.2729071896552465</v>
+        <v>0.2696582945403031</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8422,22 +8422,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2308999505602619</v>
+        <v>0.2327999505602619</v>
       </c>
       <c r="C86">
-        <v>-651.9718781976222</v>
+        <v>-665.197737508867</v>
       </c>
       <c r="D86">
-        <v>202.2921218023776</v>
+        <v>200.2872624911329</v>
       </c>
       <c r="E86">
-        <v>269.3639999999998</v>
+        <v>280.5849999999998</v>
       </c>
       <c r="F86">
-        <v>942.5639999999999</v>
+        <v>953.7849999999999</v>
       </c>
       <c r="G86">
         <v>88.3</v>
@@ -8458,37 +8458,37 @@
         <v>59.93333333333334</v>
       </c>
       <c r="M86">
-        <v>222.2565912</v>
+        <v>224.902503</v>
       </c>
       <c r="N86">
-        <v>-162.3232578666666</v>
+        <v>-164.9691696666666</v>
       </c>
       <c r="O86">
-        <v>-35.71111673066666</v>
+        <v>-36.29321732666666</v>
       </c>
       <c r="P86">
-        <v>-126.612141136</v>
+        <v>-128.67595234</v>
       </c>
       <c r="Q86">
-        <v>-52.71214113599997</v>
+        <v>-54.77595233999998</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2786158578613936</v>
+        <v>0.2941369150521533</v>
       </c>
       <c r="T86">
-        <v>5.376809650378607</v>
+        <v>5.735263627070514</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.05932482479886668</v>
+        <v>0.0586268856835859</v>
       </c>
       <c r="W86">
-        <v>0.2218112063124272</v>
+        <v>0.2219757803558104</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8496,7 +8496,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.2696582945403031</v>
+        <v>0.2664858440162996</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8504,22 +8504,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2327999505602619</v>
+        <v>0.2346999505602619</v>
       </c>
       <c r="C87">
-        <v>-665.197737508867</v>
+        <v>-678.3842476252684</v>
       </c>
       <c r="D87">
-        <v>200.2872624911329</v>
+        <v>198.3217523747315</v>
       </c>
       <c r="E87">
-        <v>280.5849999999998</v>
+        <v>291.8059999999998</v>
       </c>
       <c r="F87">
-        <v>953.7849999999999</v>
+        <v>965.0059999999999</v>
       </c>
       <c r="G87">
         <v>88.3</v>
@@ -8540,37 +8540,37 @@
         <v>59.93333333333334</v>
       </c>
       <c r="M87">
-        <v>224.902503</v>
+        <v>227.5484148</v>
       </c>
       <c r="N87">
-        <v>-164.9691696666666</v>
+        <v>-167.6150814666667</v>
       </c>
       <c r="O87">
-        <v>-36.29321732666666</v>
+        <v>-36.87531792266666</v>
       </c>
       <c r="P87">
-        <v>-128.67595234</v>
+        <v>-130.739763544</v>
       </c>
       <c r="Q87">
-        <v>-54.77595233999998</v>
+        <v>-56.83976354399999</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2941369150521533</v>
+        <v>0.3118752661273071</v>
       </c>
       <c r="T87">
-        <v>5.735263627070514</v>
+        <v>6.144925314718408</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.0586268856835859</v>
+        <v>0.05794517771052095</v>
       </c>
       <c r="W87">
-        <v>0.2219757803558104</v>
+        <v>0.2221365270958592</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8578,7 +8578,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.2664858440162996</v>
+        <v>0.2633871714114588</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8586,22 +8586,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2346999505602619</v>
+        <v>0.2365999505602619</v>
       </c>
       <c r="C88">
-        <v>-678.3842476252684</v>
+        <v>-691.5325557435672</v>
       </c>
       <c r="D88">
-        <v>198.3217523747315</v>
+        <v>196.3944442564326</v>
       </c>
       <c r="E88">
-        <v>291.8059999999998</v>
+        <v>303.0269999999998</v>
       </c>
       <c r="F88">
-        <v>965.0059999999999</v>
+        <v>976.2269999999999</v>
       </c>
       <c r="G88">
         <v>88.3</v>
@@ -8622,37 +8622,37 @@
         <v>59.93333333333334</v>
       </c>
       <c r="M88">
-        <v>227.5484148</v>
+        <v>230.1943266</v>
       </c>
       <c r="N88">
-        <v>-167.6150814666667</v>
+        <v>-170.2609932666666</v>
       </c>
       <c r="O88">
-        <v>-36.87531792266666</v>
+        <v>-37.45741851866666</v>
       </c>
       <c r="P88">
-        <v>-130.739763544</v>
+        <v>-132.803574748</v>
       </c>
       <c r="Q88">
-        <v>-56.83976354399999</v>
+        <v>-58.90357474799998</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3118752661273071</v>
+        <v>0.3323425942909461</v>
       </c>
       <c r="T88">
-        <v>6.144925314718408</v>
+        <v>6.617611877389055</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.05794517771052095</v>
+        <v>0.05727914118511266</v>
       </c>
       <c r="W88">
-        <v>0.2221365270958592</v>
+        <v>0.2222935785085504</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8660,7 +8660,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.2633871714114588</v>
+        <v>0.260359732659603</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8668,22 +8668,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2365999505602619</v>
+        <v>0.2384999505602619</v>
       </c>
       <c r="C89">
-        <v>-691.5325557435672</v>
+        <v>-704.643764895472</v>
       </c>
       <c r="D89">
-        <v>196.3944442564326</v>
+        <v>194.504235104528</v>
       </c>
       <c r="E89">
-        <v>303.0269999999998</v>
+        <v>314.2479999999999</v>
       </c>
       <c r="F89">
-        <v>976.2269999999999</v>
+        <v>987.448</v>
       </c>
       <c r="G89">
         <v>88.3</v>
@@ -8704,37 +8704,37 @@
         <v>59.93333333333334</v>
       </c>
       <c r="M89">
-        <v>230.1943266</v>
+        <v>232.8402384</v>
       </c>
       <c r="N89">
-        <v>-170.2609932666666</v>
+        <v>-172.9069050666667</v>
       </c>
       <c r="O89">
-        <v>-37.45741851866666</v>
+        <v>-38.03951911466667</v>
       </c>
       <c r="P89">
-        <v>-132.803574748</v>
+        <v>-134.867385952</v>
       </c>
       <c r="Q89">
-        <v>-58.90357474799998</v>
+        <v>-60.967385952</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3323425942909461</v>
+        <v>0.3562211438151917</v>
       </c>
       <c r="T89">
-        <v>6.617611877389055</v>
+        <v>7.169079533838144</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.05727914118511266</v>
+        <v>0.05662824185346365</v>
       </c>
       <c r="W89">
-        <v>0.2222935785085504</v>
+        <v>0.2224470605709533</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8742,7 +8742,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.260359732659603</v>
+        <v>0.2574010993339256</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8750,22 +8750,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2384999505602619</v>
+        <v>0.2403999505602619</v>
       </c>
       <c r="C90">
-        <v>-704.643764895472</v>
+        <v>-717.7189360527407</v>
       </c>
       <c r="D90">
-        <v>194.504235104528</v>
+        <v>192.6500639472593</v>
       </c>
       <c r="E90">
-        <v>314.2479999999999</v>
+        <v>325.4689999999999</v>
       </c>
       <c r="F90">
-        <v>987.448</v>
+        <v>998.669</v>
       </c>
       <c r="G90">
         <v>88.3</v>
@@ -8786,37 +8786,37 @@
         <v>59.93333333333334</v>
       </c>
       <c r="M90">
-        <v>232.8402384</v>
+        <v>235.4861502</v>
       </c>
       <c r="N90">
-        <v>-172.9069050666667</v>
+        <v>-175.5528168666667</v>
       </c>
       <c r="O90">
-        <v>-38.03951911466667</v>
+        <v>-38.62161971066666</v>
       </c>
       <c r="P90">
-        <v>-134.867385952</v>
+        <v>-136.931197156</v>
       </c>
       <c r="Q90">
-        <v>-60.967385952</v>
+        <v>-63.03119715599999</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3562211438151917</v>
+        <v>0.3844412477983909</v>
       </c>
       <c r="T90">
-        <v>7.169079533838144</v>
+        <v>7.82081403691434</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.05662824185346365</v>
+        <v>0.05599196947308765</v>
       </c>
       <c r="W90">
-        <v>0.2224470605709533</v>
+        <v>0.2225970935982459</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8824,7 +8824,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.2574010993339256</v>
+        <v>0.2545089521503985</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8832,22 +8832,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2403999505602619</v>
+        <v>0.2422999505602619</v>
       </c>
       <c r="C91">
-        <v>-717.7189360527407</v>
+        <v>-730.7590901129992</v>
       </c>
       <c r="D91">
-        <v>192.6500639472593</v>
+        <v>190.8309098870008</v>
       </c>
       <c r="E91">
-        <v>325.4689999999999</v>
+        <v>336.6899999999999</v>
       </c>
       <c r="F91">
-        <v>998.669</v>
+        <v>1009.89</v>
       </c>
       <c r="G91">
         <v>88.3</v>
@@ -8868,37 +8868,37 @@
         <v>59.93333333333334</v>
       </c>
       <c r="M91">
-        <v>235.4861502</v>
+        <v>238.132062</v>
       </c>
       <c r="N91">
-        <v>-175.5528168666667</v>
+        <v>-178.1987286666667</v>
       </c>
       <c r="O91">
-        <v>-38.62161971066666</v>
+        <v>-39.20372030666667</v>
       </c>
       <c r="P91">
-        <v>-136.931197156</v>
+        <v>-138.99500836</v>
       </c>
       <c r="Q91">
-        <v>-63.03119715599999</v>
+        <v>-65.09500836000001</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.3844412477983909</v>
+        <v>0.41830537257823</v>
       </c>
       <c r="T91">
-        <v>7.82081403691434</v>
+        <v>8.602895440605774</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.05599196947308765</v>
+        <v>0.05536983647894223</v>
       </c>
       <c r="W91">
-        <v>0.2225970935982459</v>
+        <v>0.2227437925582654</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8906,7 +8906,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.2545089521503985</v>
+        <v>0.2516810749042828</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8914,22 +8914,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2422999505602619</v>
+        <v>0.2441999505602619</v>
       </c>
       <c r="C92">
-        <v>-730.7590901129992</v>
+        <v>-743.7652097740979</v>
       </c>
       <c r="D92">
-        <v>190.8309098870008</v>
+        <v>189.045790225902</v>
       </c>
       <c r="E92">
-        <v>336.6899999999999</v>
+        <v>347.9109999999999</v>
       </c>
       <c r="F92">
-        <v>1009.89</v>
+        <v>1021.111</v>
       </c>
       <c r="G92">
         <v>88.3</v>
@@ -8950,37 +8950,37 @@
         <v>59.93333333333334</v>
       </c>
       <c r="M92">
-        <v>238.132062</v>
+        <v>240.7779738</v>
       </c>
       <c r="N92">
-        <v>-178.1987286666667</v>
+        <v>-180.8446404666667</v>
       </c>
       <c r="O92">
-        <v>-39.20372030666667</v>
+        <v>-39.78582090266667</v>
       </c>
       <c r="P92">
-        <v>-138.99500836</v>
+        <v>-141.058819564</v>
       </c>
       <c r="Q92">
-        <v>-65.09500836000001</v>
+        <v>-67.158819564</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.41830537257823</v>
+        <v>0.4596948584202556</v>
       </c>
       <c r="T92">
-        <v>8.602895440605774</v>
+        <v>9.558772711784194</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.05536983647894223</v>
+        <v>0.0547613767374154</v>
       </c>
       <c r="W92">
-        <v>0.2227437925582654</v>
+        <v>0.2228872673653174</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8988,7 +8988,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.2516810749042828</v>
+        <v>0.2489153488064336</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8996,22 +8996,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2441999505602619</v>
+        <v>0.2460999505602618</v>
       </c>
       <c r="C93">
-        <v>-743.7652097740979</v>
+        <v>-756.738241304246</v>
       </c>
       <c r="D93">
-        <v>189.045790225902</v>
+        <v>187.2937586957539</v>
       </c>
       <c r="E93">
-        <v>347.9109999999999</v>
+        <v>359.1319999999998</v>
       </c>
       <c r="F93">
-        <v>1021.111</v>
+        <v>1032.332</v>
       </c>
       <c r="G93">
         <v>88.3</v>
@@ -9032,37 +9032,37 @@
         <v>59.93333333333334</v>
       </c>
       <c r="M93">
-        <v>240.7779738</v>
+        <v>243.4238856</v>
       </c>
       <c r="N93">
-        <v>-180.8446404666667</v>
+        <v>-183.4905522666666</v>
       </c>
       <c r="O93">
-        <v>-39.78582090266667</v>
+        <v>-40.36792149866666</v>
       </c>
       <c r="P93">
-        <v>-141.058819564</v>
+        <v>-143.122630768</v>
       </c>
       <c r="Q93">
-        <v>-67.158819564</v>
+        <v>-69.22263076799996</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.4596948584202556</v>
+        <v>0.5114317157227877</v>
       </c>
       <c r="T93">
-        <v>9.558772711784194</v>
+        <v>10.75361930075722</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.0547613767374154</v>
+        <v>0.05416614438157393</v>
       </c>
       <c r="W93">
-        <v>0.2228872673653174</v>
+        <v>0.2230276231548249</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -9070,7 +9070,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.2489153488064336</v>
+        <v>0.2462097471889724</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9078,22 +9078,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2460999505602618</v>
+        <v>0.2479999505602619</v>
       </c>
       <c r="C94">
-        <v>-756.738241304246</v>
+        <v>-769.6790962146154</v>
       </c>
       <c r="D94">
-        <v>187.2937586957539</v>
+        <v>185.5739037853846</v>
       </c>
       <c r="E94">
-        <v>359.1319999999998</v>
+        <v>370.3529999999998</v>
       </c>
       <c r="F94">
-        <v>1032.332</v>
+        <v>1043.553</v>
       </c>
       <c r="G94">
         <v>88.3</v>
@@ -9114,37 +9114,37 @@
         <v>59.93333333333334</v>
       </c>
       <c r="M94">
-        <v>243.4238856</v>
+        <v>246.0697974</v>
       </c>
       <c r="N94">
-        <v>-183.4905522666666</v>
+        <v>-186.1364640666666</v>
       </c>
       <c r="O94">
-        <v>-40.36792149866666</v>
+        <v>-40.95002209466666</v>
       </c>
       <c r="P94">
-        <v>-143.122630768</v>
+        <v>-145.186441972</v>
       </c>
       <c r="Q94">
-        <v>-69.22263076799996</v>
+        <v>-71.28644197199998</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.5114317157227877</v>
+        <v>0.5779505322546145</v>
       </c>
       <c r="T94">
-        <v>10.75361930075722</v>
+        <v>12.28985062943683</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.05416614438157393</v>
+        <v>0.05358371272155701</v>
       </c>
       <c r="W94">
-        <v>0.2230276231548249</v>
+        <v>0.2231649605402569</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9152,7 +9152,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.2462097471889724</v>
+        <v>0.2435623305525318</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9160,22 +9160,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2479999505602619</v>
+        <v>0.2498999505602619</v>
       </c>
       <c r="C95">
-        <v>-769.6790962146154</v>
+        <v>-782.5886528406305</v>
       </c>
       <c r="D95">
-        <v>185.5739037853846</v>
+        <v>183.8853471593694</v>
       </c>
       <c r="E95">
-        <v>370.3529999999998</v>
+        <v>381.5739999999998</v>
       </c>
       <c r="F95">
-        <v>1043.553</v>
+        <v>1054.774</v>
       </c>
       <c r="G95">
         <v>88.3</v>
@@ -9196,37 +9196,37 @@
         <v>59.93333333333334</v>
       </c>
       <c r="M95">
-        <v>246.0697974</v>
+        <v>248.7157092</v>
       </c>
       <c r="N95">
-        <v>-186.1364640666666</v>
+        <v>-188.7823758666667</v>
       </c>
       <c r="O95">
-        <v>-40.95002209466666</v>
+        <v>-41.53212269066666</v>
       </c>
       <c r="P95">
-        <v>-145.186441972</v>
+        <v>-147.250253176</v>
       </c>
       <c r="Q95">
-        <v>-71.28644197199998</v>
+        <v>-73.350253176</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.5779505322546145</v>
+        <v>0.6666422876303837</v>
       </c>
       <c r="T95">
-        <v>12.28985062943683</v>
+        <v>14.3381590676763</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.05358371272155701</v>
+        <v>0.05301367322451916</v>
       </c>
       <c r="W95">
-        <v>0.2231649605402569</v>
+        <v>0.2232993758536584</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9234,7 +9234,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.2435623305525318</v>
+        <v>0.2409712419296326</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9242,22 +9242,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2498999505602619</v>
+        <v>0.2517999505602619</v>
       </c>
       <c r="C96">
-        <v>-782.5886528406305</v>
+        <v>-795.4677578377075</v>
       </c>
       <c r="D96">
-        <v>183.8853471593694</v>
+        <v>182.2272421622924</v>
       </c>
       <c r="E96">
-        <v>381.5739999999998</v>
+        <v>392.7949999999998</v>
       </c>
       <c r="F96">
-        <v>1054.774</v>
+        <v>1065.995</v>
       </c>
       <c r="G96">
         <v>88.3</v>
@@ -9278,37 +9278,37 @@
         <v>59.93333333333334</v>
       </c>
       <c r="M96">
-        <v>248.7157092</v>
+        <v>251.361621</v>
       </c>
       <c r="N96">
-        <v>-188.7823758666667</v>
+        <v>-191.4282876666666</v>
       </c>
       <c r="O96">
-        <v>-41.53212269066666</v>
+        <v>-42.11422328666666</v>
       </c>
       <c r="P96">
-        <v>-147.250253176</v>
+        <v>-149.31406438</v>
       </c>
       <c r="Q96">
-        <v>-73.350253176</v>
+        <v>-75.41406437999999</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.6666422876303837</v>
+        <v>0.7908107451564609</v>
       </c>
       <c r="T96">
-        <v>14.3381590676763</v>
+        <v>17.20579088121157</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.05301367322451916</v>
+        <v>0.05245563455899791</v>
       </c>
       <c r="W96">
-        <v>0.2232993758536584</v>
+        <v>0.2234309613709883</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9316,7 +9316,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.2409712419296326</v>
+        <v>0.2384347025408996</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9324,22 +9324,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2517999505602619</v>
+        <v>0.2536999505602619</v>
       </c>
       <c r="C97">
-        <v>-795.4677578377075</v>
+        <v>-808.3172275967917</v>
       </c>
       <c r="D97">
-        <v>182.2272421622924</v>
+        <v>180.5987724032082</v>
       </c>
       <c r="E97">
-        <v>392.7949999999998</v>
+        <v>404.0159999999998</v>
       </c>
       <c r="F97">
-        <v>1065.995</v>
+        <v>1077.216</v>
       </c>
       <c r="G97">
         <v>88.3</v>
@@ -9360,37 +9360,37 @@
         <v>59.93333333333334</v>
       </c>
       <c r="M97">
-        <v>251.361621</v>
+        <v>254.0075328</v>
       </c>
       <c r="N97">
-        <v>-191.4282876666666</v>
+        <v>-194.0741994666666</v>
       </c>
       <c r="O97">
-        <v>-42.11422328666666</v>
+        <v>-42.69632388266666</v>
       </c>
       <c r="P97">
-        <v>-149.31406438</v>
+        <v>-151.377875584</v>
       </c>
       <c r="Q97">
-        <v>-75.41406437999999</v>
+        <v>-77.47787558399997</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.7908107451564609</v>
+        <v>0.9770634314455766</v>
       </c>
       <c r="T97">
-        <v>17.20579088121157</v>
+        <v>21.50723860151447</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.05245563455899791</v>
+        <v>0.05190922169900835</v>
       </c>
       <c r="W97">
-        <v>0.2234309613709883</v>
+        <v>0.2235598055233738</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9398,7 +9398,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.2384347025408996</v>
+        <v>0.2359510077227652</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9406,22 +9406,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2536999505602619</v>
+        <v>0.2555999505602619</v>
       </c>
       <c r="C98">
-        <v>-808.3172275967917</v>
+        <v>-821.1378495846694</v>
       </c>
       <c r="D98">
-        <v>180.5987724032082</v>
+        <v>178.9991504153305</v>
       </c>
       <c r="E98">
-        <v>404.0159999999998</v>
+        <v>415.2369999999999</v>
       </c>
       <c r="F98">
-        <v>1077.216</v>
+        <v>1088.437</v>
       </c>
       <c r="G98">
         <v>88.3</v>
@@ -9442,37 +9442,37 @@
         <v>59.93333333333334</v>
       </c>
       <c r="M98">
-        <v>254.0075328</v>
+        <v>256.6534446</v>
       </c>
       <c r="N98">
-        <v>-194.0741994666666</v>
+        <v>-196.7201112666667</v>
       </c>
       <c r="O98">
-        <v>-42.69632388266666</v>
+        <v>-43.27842447866666</v>
       </c>
       <c r="P98">
-        <v>-151.377875584</v>
+        <v>-153.441686788</v>
       </c>
       <c r="Q98">
-        <v>-77.47787558399997</v>
+        <v>-79.54168678799999</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.9770634314455739</v>
+        <v>1.287484575260766</v>
       </c>
       <c r="T98">
-        <v>21.50723860151441</v>
+        <v>28.67631813535256</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.05190922169900835</v>
+        <v>0.05137407508355465</v>
       </c>
       <c r="W98">
-        <v>0.2235598055233738</v>
+        <v>0.2236859930952978</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9480,7 +9480,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.2359510077227652</v>
+        <v>0.2335185231070666</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9488,22 +9488,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2555999505602619</v>
+        <v>0.2574999505602619</v>
       </c>
       <c r="C99">
-        <v>-821.1378495846694</v>
+        <v>-833.9303836136751</v>
       </c>
       <c r="D99">
-        <v>178.9991504153305</v>
+        <v>177.4276163863248</v>
       </c>
       <c r="E99">
-        <v>415.2369999999999</v>
+        <v>426.4579999999999</v>
       </c>
       <c r="F99">
-        <v>1088.437</v>
+        <v>1099.658</v>
       </c>
       <c r="G99">
         <v>88.3</v>
@@ -9524,37 +9524,37 @@
         <v>59.93333333333334</v>
       </c>
       <c r="M99">
-        <v>256.6534446</v>
+        <v>259.2993564</v>
       </c>
       <c r="N99">
-        <v>-196.7201112666667</v>
+        <v>-199.3660230666666</v>
       </c>
       <c r="O99">
-        <v>-43.27842447866666</v>
+        <v>-43.86052507466666</v>
       </c>
       <c r="P99">
-        <v>-153.441686788</v>
+        <v>-155.505497992</v>
       </c>
       <c r="Q99">
-        <v>-79.54168678799999</v>
+        <v>-81.60549799199995</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.287484575260766</v>
+        <v>1.908326862891148</v>
       </c>
       <c r="T99">
-        <v>28.67631813535256</v>
+        <v>43.01447720302883</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.05137407508355465</v>
+        <v>0.05084984982760002</v>
       </c>
       <c r="W99">
-        <v>0.2236859930952978</v>
+        <v>0.2238096054106519</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9562,7 +9562,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.2335185231070666</v>
+        <v>0.2311356810345455</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9570,22 +9570,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2574999505602619</v>
+        <v>0.2593999505602619</v>
       </c>
       <c r="C100">
-        <v>-833.9303836136751</v>
+        <v>-846.6955630450957</v>
       </c>
       <c r="D100">
-        <v>177.4276163863248</v>
+        <v>175.8834369549042</v>
       </c>
       <c r="E100">
-        <v>426.4579999999999</v>
+        <v>437.6789999999999</v>
       </c>
       <c r="F100">
-        <v>1099.658</v>
+        <v>1110.879</v>
       </c>
       <c r="G100">
         <v>88.3</v>
@@ -9606,37 +9606,37 @@
         <v>59.93333333333334</v>
       </c>
       <c r="M100">
-        <v>259.2993564</v>
+        <v>261.9452682</v>
       </c>
       <c r="N100">
-        <v>-199.3660230666666</v>
+        <v>-202.0119348666666</v>
       </c>
       <c r="O100">
-        <v>-43.86052507466666</v>
+        <v>-44.44262567066666</v>
       </c>
       <c r="P100">
-        <v>-155.505497992</v>
+        <v>-157.569309196</v>
       </c>
       <c r="Q100">
-        <v>-81.60549799199995</v>
+        <v>-83.66930919599997</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.908326862891148</v>
+        <v>3.770853725782296</v>
       </c>
       <c r="T100">
-        <v>43.01447720302883</v>
+        <v>86.02895440605765</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.05084984982760002</v>
+        <v>0.05033621498085658</v>
       </c>
       <c r="W100">
-        <v>0.2238096054106519</v>
+        <v>0.223930720507514</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9644,91 +9644,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.2311356810345455</v>
+        <v>0.2288009771857117</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2593999505602619</v>
-      </c>
-      <c r="C101">
-        <v>-846.6955630450957</v>
-      </c>
-      <c r="D101">
-        <v>175.8834369549042</v>
-      </c>
-      <c r="E101">
-        <v>437.6789999999999</v>
-      </c>
-      <c r="F101">
-        <v>1110.879</v>
-      </c>
-      <c r="G101">
-        <v>88.3</v>
-      </c>
-      <c r="H101">
-        <v>448.9</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>133.8333333333333</v>
-      </c>
-      <c r="K101">
-        <v>73.90000000000001</v>
-      </c>
-      <c r="L101">
-        <v>59.93333333333334</v>
-      </c>
-      <c r="M101">
-        <v>261.9452682</v>
-      </c>
-      <c r="N101">
-        <v>-202.0119348666666</v>
-      </c>
-      <c r="O101">
-        <v>-44.44262567066666</v>
-      </c>
-      <c r="P101">
-        <v>-157.569309196</v>
-      </c>
-      <c r="Q101">
-        <v>-83.66930919599997</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.770853725782296</v>
-      </c>
-      <c r="T101">
-        <v>86.02895440605765</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.05033621498085658</v>
-      </c>
-      <c r="W101">
-        <v>0.223930720507514</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.2288009771857117</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
